--- a/downloads/rajasthan.xlsx
+++ b/downloads/rajasthan.xlsx
@@ -9084,7 +9084,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Marwar Junciton</t>
+          <t>Marwar Junction</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">

--- a/downloads/rajasthan.xlsx
+++ b/downloads/rajasthan.xlsx
@@ -842,16 +842,16 @@
         <v>1724</v>
       </c>
       <c r="G2" t="n">
-        <v>0.72</v>
+        <v>0.7201</v>
       </c>
       <c r="H2" t="n">
-        <v>47.79</v>
+        <v>47.7917</v>
       </c>
       <c r="I2" t="n">
-        <v>47.76</v>
+        <v>47.758</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.03</v>
+        <v>-0.0337</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>198085</v>
       </c>
       <c r="O2" t="n">
-        <v>82.63</v>
+        <v>82.6349</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -912,16 +912,16 @@
         <v>10707</v>
       </c>
       <c r="G3" t="n">
-        <v>4.48</v>
+        <v>4.4809</v>
       </c>
       <c r="H3" t="n">
-        <v>47.94</v>
+        <v>47.942</v>
       </c>
       <c r="I3" t="n">
-        <v>48</v>
+        <v>47.9964</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05</v>
+        <v>0.0544</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>181386</v>
       </c>
       <c r="O3" t="n">
-        <v>75.84</v>
+        <v>75.8439</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -982,16 +982,16 @@
         <v>-739</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.31</v>
+        <v>-0.3069</v>
       </c>
       <c r="H4" t="n">
-        <v>47.74</v>
+        <v>47.7424</v>
       </c>
       <c r="I4" t="n">
-        <v>47.94</v>
+        <v>47.9436</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2</v>
+        <v>0.2013</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>195586</v>
       </c>
       <c r="O4" t="n">
-        <v>81.15000000000001</v>
+        <v>81.154</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -1052,16 +1052,16 @@
         <v>-3421</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.34</v>
+        <v>-1.3368</v>
       </c>
       <c r="H5" t="n">
-        <v>47.22</v>
+        <v>47.2231</v>
       </c>
       <c r="I5" t="n">
-        <v>47.51</v>
+        <v>47.5098</v>
       </c>
       <c r="J5" t="n">
-        <v>0.29</v>
+        <v>0.2867</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>209143</v>
       </c>
       <c r="O5" t="n">
-        <v>81.63</v>
+        <v>81.63209999999999</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1122,16 +1122,16 @@
         <v>-539</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2</v>
+        <v>-0.2009</v>
       </c>
       <c r="H6" t="n">
-        <v>47.48</v>
+        <v>47.483</v>
       </c>
       <c r="I6" t="n">
-        <v>47.57</v>
+        <v>47.5663</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08</v>
+        <v>0.0833</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>214655</v>
       </c>
       <c r="O6" t="n">
-        <v>79.89</v>
+        <v>79.8874</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1192,16 +1192,16 @@
         <v>2521</v>
       </c>
       <c r="G7" t="n">
-        <v>1.03</v>
+        <v>1.026</v>
       </c>
       <c r="H7" t="n">
-        <v>47.33</v>
+        <v>47.3299</v>
       </c>
       <c r="I7" t="n">
-        <v>47.37</v>
+        <v>47.3678</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04</v>
+        <v>0.0379</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>193192</v>
       </c>
       <c r="O7" t="n">
-        <v>78.55</v>
+        <v>78.5467</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1262,16 +1262,16 @@
         <v>-1880</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.76</v>
+        <v>-0.7645</v>
       </c>
       <c r="H8" t="n">
-        <v>47.97</v>
+        <v>47.9698</v>
       </c>
       <c r="I8" t="n">
-        <v>47.85</v>
+        <v>47.8488</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.12</v>
+        <v>-0.121</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>207478</v>
       </c>
       <c r="O8" t="n">
-        <v>84.3</v>
+        <v>84.3006</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1332,16 +1332,16 @@
         <v>6268</v>
       </c>
       <c r="G9" t="n">
-        <v>2.11</v>
+        <v>2.1065</v>
       </c>
       <c r="H9" t="n">
-        <v>48.15</v>
+        <v>48.1472</v>
       </c>
       <c r="I9" t="n">
-        <v>47.97</v>
+        <v>47.968</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.18</v>
+        <v>-0.1793</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>241223</v>
       </c>
       <c r="O9" t="n">
-        <v>81.01000000000001</v>
+        <v>81.00790000000001</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1402,16 +1402,16 @@
         <v>1041</v>
       </c>
       <c r="G10" t="n">
-        <v>0.35</v>
+        <v>0.3508</v>
       </c>
       <c r="H10" t="n">
-        <v>47.94</v>
+        <v>47.9359</v>
       </c>
       <c r="I10" t="n">
-        <v>47.79</v>
+        <v>47.7882</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.15</v>
+        <v>-0.1478</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>247404</v>
       </c>
       <c r="O10" t="n">
-        <v>83.3</v>
+        <v>83.30070000000001</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>-2559</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.91</v>
+        <v>-0.9116</v>
       </c>
       <c r="H11" t="n">
-        <v>47.19</v>
+        <v>47.1935</v>
       </c>
       <c r="I11" t="n">
-        <v>47.25</v>
+        <v>47.2462</v>
       </c>
       <c r="J11" t="n">
-        <v>0.05</v>
+        <v>0.0527</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>239758</v>
       </c>
       <c r="O11" t="n">
-        <v>85.25</v>
+        <v>85.2518</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1542,16 +1542,16 @@
         <v>2186</v>
       </c>
       <c r="G12" t="n">
-        <v>0.79</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>47.51</v>
+        <v>47.5053</v>
       </c>
       <c r="I12" t="n">
-        <v>47.32</v>
+        <v>47.3182</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.19</v>
+        <v>-0.1871</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>229969</v>
       </c>
       <c r="O12" t="n">
-        <v>83.20999999999999</v>
+        <v>83.21210000000001</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>8231</v>
       </c>
       <c r="G13" t="n">
-        <v>3.48</v>
+        <v>3.4782</v>
       </c>
       <c r="H13" t="n">
-        <v>46.99</v>
+        <v>46.9913</v>
       </c>
       <c r="I13" t="n">
-        <v>46.53</v>
+        <v>46.5315</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.46</v>
+        <v>-0.4598</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>177351</v>
       </c>
       <c r="O13" t="n">
-        <v>74.88</v>
+        <v>74.88160000000001</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1682,16 +1682,16 @@
         <v>11505</v>
       </c>
       <c r="G14" t="n">
-        <v>4.84</v>
+        <v>4.842</v>
       </c>
       <c r="H14" t="n">
-        <v>48.63</v>
+        <v>48.6326</v>
       </c>
       <c r="I14" t="n">
-        <v>48.25</v>
+        <v>48.2488</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.38</v>
+        <v>-0.3838</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>180983</v>
       </c>
       <c r="O14" t="n">
-        <v>76.14</v>
+        <v>76.14279999999999</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1752,16 +1752,16 @@
         <v>22808</v>
       </c>
       <c r="G15" t="n">
-        <v>9.220000000000001</v>
+        <v>9.2219</v>
       </c>
       <c r="H15" t="n">
-        <v>48.95</v>
+        <v>48.9498</v>
       </c>
       <c r="I15" t="n">
-        <v>48.64</v>
+        <v>48.644</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.31</v>
+        <v>-0.3058</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>169422</v>
       </c>
       <c r="O15" t="n">
-        <v>68.40000000000001</v>
+        <v>68.3994</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1822,16 +1822,16 @@
         <v>-118</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.05</v>
+        <v>-0.0461</v>
       </c>
       <c r="H16" t="n">
-        <v>46.39</v>
+        <v>46.3924</v>
       </c>
       <c r="I16" t="n">
-        <v>46.4</v>
+        <v>46.405</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01</v>
+        <v>0.0126</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>202018</v>
       </c>
       <c r="O16" t="n">
-        <v>78.86</v>
+        <v>78.8566</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1892,16 +1892,16 @@
         <v>-5946</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.28</v>
+        <v>-2.2815</v>
       </c>
       <c r="H17" t="n">
-        <v>46.81</v>
+        <v>46.807</v>
       </c>
       <c r="I17" t="n">
-        <v>47.33</v>
+        <v>47.3303</v>
       </c>
       <c r="J17" t="n">
-        <v>0.52</v>
+        <v>0.5233</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>201592</v>
       </c>
       <c r="O17" t="n">
-        <v>77.27</v>
+        <v>77.2709</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1962,16 +1962,16 @@
         <v>-1152</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.43</v>
+        <v>-0.4332</v>
       </c>
       <c r="H18" t="n">
-        <v>46.97</v>
+        <v>46.9736</v>
       </c>
       <c r="I18" t="n">
-        <v>46.92</v>
+        <v>46.9178</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.06</v>
+        <v>-0.0558</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>201837</v>
       </c>
       <c r="O18" t="n">
-        <v>75.8</v>
+        <v>75.7976</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -2032,16 +2032,16 @@
         <v>304</v>
       </c>
       <c r="G19" t="n">
-        <v>0.11</v>
+        <v>0.1078</v>
       </c>
       <c r="H19" t="n">
-        <v>46.61</v>
+        <v>46.6129</v>
       </c>
       <c r="I19" t="n">
-        <v>46.43</v>
+        <v>46.429</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.18</v>
+        <v>-0.184</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>214108</v>
       </c>
       <c r="O19" t="n">
-        <v>75.78</v>
+        <v>75.7786</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -2102,16 +2102,16 @@
         <v>667</v>
       </c>
       <c r="G20" t="n">
-        <v>0.27</v>
+        <v>0.2685</v>
       </c>
       <c r="H20" t="n">
-        <v>48.15</v>
+        <v>48.1549</v>
       </c>
       <c r="I20" t="n">
-        <v>47.85</v>
+        <v>47.8451</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.31</v>
+        <v>-0.3099</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>195540</v>
       </c>
       <c r="O20" t="n">
-        <v>77.88</v>
+        <v>77.8811</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -2172,16 +2172,16 @@
         <v>-393</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.15</v>
+        <v>-0.1502</v>
       </c>
       <c r="H21" t="n">
-        <v>47.64</v>
+        <v>47.6388</v>
       </c>
       <c r="I21" t="n">
-        <v>47.35</v>
+        <v>47.3509</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.29</v>
+        <v>-0.2879</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>218591</v>
       </c>
       <c r="O21" t="n">
-        <v>83.04000000000001</v>
+        <v>83.0444</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2242,16 +2242,16 @@
         <v>3667</v>
       </c>
       <c r="G22" t="n">
-        <v>1.2</v>
+        <v>1.201</v>
       </c>
       <c r="H22" t="n">
-        <v>47.46</v>
+        <v>47.4618</v>
       </c>
       <c r="I22" t="n">
-        <v>47.04</v>
+        <v>47.0366</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.43</v>
+        <v>-0.4252</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>235583</v>
       </c>
       <c r="O22" t="n">
-        <v>77.03</v>
+        <v>77.0312</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -2312,16 +2312,16 @@
         <v>2899</v>
       </c>
       <c r="G23" t="n">
-        <v>1.13</v>
+        <v>1.1347</v>
       </c>
       <c r="H23" t="n">
-        <v>48.36</v>
+        <v>48.3596</v>
       </c>
       <c r="I23" t="n">
-        <v>47.82</v>
+        <v>47.8156</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.54</v>
+        <v>-0.544</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>198681</v>
       </c>
       <c r="O23" t="n">
-        <v>77.41</v>
+        <v>77.4081</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -2382,16 +2382,16 @@
         <v>3357</v>
       </c>
       <c r="G24" t="n">
-        <v>1.21</v>
+        <v>1.2089</v>
       </c>
       <c r="H24" t="n">
-        <v>47.89</v>
+        <v>47.8946</v>
       </c>
       <c r="I24" t="n">
         <v>47.39</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5</v>
+        <v>-0.5046</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>203735</v>
       </c>
       <c r="O24" t="n">
-        <v>73.15000000000001</v>
+        <v>73.15260000000001</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -2452,16 +2452,16 @@
         <v>733</v>
       </c>
       <c r="G25" t="n">
-        <v>0.25</v>
+        <v>0.2535</v>
       </c>
       <c r="H25" t="n">
-        <v>47.66</v>
+        <v>47.6579</v>
       </c>
       <c r="I25" t="n">
-        <v>47.25</v>
+        <v>47.2512</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.41</v>
+        <v>-0.4066</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>200989</v>
       </c>
       <c r="O25" t="n">
-        <v>69.42</v>
+        <v>69.4248</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -2522,16 +2522,16 @@
         <v>3336</v>
       </c>
       <c r="G26" t="n">
-        <v>1.35</v>
+        <v>1.3522</v>
       </c>
       <c r="H26" t="n">
-        <v>47.91</v>
+        <v>47.914</v>
       </c>
       <c r="I26" t="n">
-        <v>47.44</v>
+        <v>47.4429</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.47</v>
+        <v>-0.4711</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>172747</v>
       </c>
       <c r="O26" t="n">
-        <v>69.22</v>
+        <v>69.21980000000001</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2592,16 +2592,16 @@
         <v>7862</v>
       </c>
       <c r="G27" t="n">
-        <v>2.77</v>
+        <v>2.7745</v>
       </c>
       <c r="H27" t="n">
-        <v>47.79</v>
+        <v>47.7944</v>
       </c>
       <c r="I27" t="n">
-        <v>47.15</v>
+        <v>47.1496</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.64</v>
+        <v>-0.6448</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>200348</v>
       </c>
       <c r="O27" t="n">
-        <v>68.73999999999999</v>
+        <v>68.7373</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -2662,16 +2662,16 @@
         <v>5170</v>
       </c>
       <c r="G28" t="n">
-        <v>1.92</v>
+        <v>1.9226</v>
       </c>
       <c r="H28" t="n">
-        <v>47.89</v>
+        <v>47.8857</v>
       </c>
       <c r="I28" t="n">
-        <v>47.42</v>
+        <v>47.4155</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.47</v>
+        <v>-0.4703</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>195142</v>
       </c>
       <c r="O28" t="n">
-        <v>71.65000000000001</v>
+        <v>71.64879999999999</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2732,16 +2732,16 @@
         <v>2538</v>
       </c>
       <c r="G29" t="n">
-        <v>1.03</v>
+        <v>1.0332</v>
       </c>
       <c r="H29" t="n">
-        <v>48.06</v>
+        <v>48.055</v>
       </c>
       <c r="I29" t="n">
-        <v>47.6</v>
+        <v>47.602</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.45</v>
+        <v>-0.4531</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>185232</v>
       </c>
       <c r="O29" t="n">
-        <v>74.53</v>
+        <v>74.5253</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -2802,16 +2802,16 @@
         <v>4202</v>
       </c>
       <c r="G30" t="n">
-        <v>1.51</v>
+        <v>1.5109</v>
       </c>
       <c r="H30" t="n">
-        <v>47.77</v>
+        <v>47.7702</v>
       </c>
       <c r="I30" t="n">
-        <v>47.24</v>
+        <v>47.2417</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.53</v>
+        <v>-0.5285</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>207626</v>
       </c>
       <c r="O30" t="n">
-        <v>73.98999999999999</v>
+        <v>73.9888</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -2872,16 +2872,16 @@
         <v>5894</v>
       </c>
       <c r="G31" t="n">
-        <v>2.3</v>
+        <v>2.2999</v>
       </c>
       <c r="H31" t="n">
-        <v>47.44</v>
+        <v>47.4384</v>
       </c>
       <c r="I31" t="n">
-        <v>46.86</v>
+        <v>46.8621</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.58</v>
+        <v>-0.5763</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>199059</v>
       </c>
       <c r="O31" t="n">
-        <v>76.56999999999999</v>
+        <v>76.5718</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -2942,16 +2942,16 @@
         <v>2645</v>
       </c>
       <c r="G32" t="n">
-        <v>1.19</v>
+        <v>1.1856</v>
       </c>
       <c r="H32" t="n">
-        <v>47.06</v>
+        <v>47.0602</v>
       </c>
       <c r="I32" t="n">
-        <v>46.54</v>
+        <v>46.5416</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.52</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>168825</v>
       </c>
       <c r="O32" t="n">
-        <v>74.09</v>
+        <v>74.0941</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -3012,16 +3012,16 @@
         <v>3663</v>
       </c>
       <c r="G33" t="n">
-        <v>1.45</v>
+        <v>1.4454</v>
       </c>
       <c r="H33" t="n">
-        <v>47.79</v>
+        <v>47.7856</v>
       </c>
       <c r="I33" t="n">
-        <v>47.47</v>
+        <v>47.4746</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.31</v>
+        <v>-0.3109</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>181512</v>
       </c>
       <c r="O33" t="n">
-        <v>71.23999999999999</v>
+        <v>71.2384</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -3082,16 +3082,16 @@
         <v>5207</v>
       </c>
       <c r="G34" t="n">
-        <v>1.87</v>
+        <v>1.8721</v>
       </c>
       <c r="H34" t="n">
-        <v>48.59</v>
+        <v>48.586</v>
       </c>
       <c r="I34" t="n">
-        <v>47.89</v>
+        <v>47.8938</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.6922</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>215757</v>
       </c>
       <c r="O34" t="n">
-        <v>77.05</v>
+        <v>77.0484</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -3152,16 +3152,16 @@
         <v>3180</v>
       </c>
       <c r="G35" t="n">
-        <v>1.15</v>
+        <v>1.1484</v>
       </c>
       <c r="H35" t="n">
-        <v>48.18</v>
+        <v>48.1759</v>
       </c>
       <c r="I35" t="n">
-        <v>47.77</v>
+        <v>47.7707</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.41</v>
+        <v>-0.4052</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>202223</v>
       </c>
       <c r="O35" t="n">
-        <v>72.45</v>
+        <v>72.4481</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -3222,16 +3222,16 @@
         <v>7709</v>
       </c>
       <c r="G36" t="n">
-        <v>2.66</v>
+        <v>2.6627</v>
       </c>
       <c r="H36" t="n">
-        <v>47.6</v>
+        <v>47.6041</v>
       </c>
       <c r="I36" t="n">
-        <v>47.34</v>
+        <v>47.3383</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.27</v>
+        <v>-0.2659</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>213541</v>
       </c>
       <c r="O36" t="n">
-        <v>73.47</v>
+        <v>73.4747</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -3292,16 +3292,16 @@
         <v>2040</v>
       </c>
       <c r="G37" t="n">
-        <v>0.71</v>
+        <v>0.7083</v>
       </c>
       <c r="H37" t="n">
-        <v>48.02</v>
+        <v>48.0214</v>
       </c>
       <c r="I37" t="n">
-        <v>47.73</v>
+        <v>47.7279</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.29</v>
+        <v>-0.2935</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>220759</v>
       </c>
       <c r="O37" t="n">
-        <v>76.13</v>
+        <v>76.1285</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -3362,16 +3362,16 @@
         <v>2411</v>
       </c>
       <c r="G38" t="n">
-        <v>0.91</v>
+        <v>0.9101</v>
       </c>
       <c r="H38" t="n">
-        <v>47.47</v>
+        <v>47.4723</v>
       </c>
       <c r="I38" t="n">
-        <v>47.18</v>
+        <v>47.1807</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.29</v>
+        <v>-0.2916</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>204003</v>
       </c>
       <c r="O38" t="n">
-        <v>76.26000000000001</v>
+        <v>76.2617</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -3432,16 +3432,16 @@
         <v>2305</v>
       </c>
       <c r="G39" t="n">
-        <v>0.85</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>46.91</v>
+        <v>46.9092</v>
       </c>
       <c r="I39" t="n">
-        <v>46.64</v>
+        <v>46.6405</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.27</v>
+        <v>-0.2687</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>197675</v>
       </c>
       <c r="O39" t="n">
-        <v>72.15000000000001</v>
+        <v>72.15179999999999</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -3502,16 +3502,16 @@
         <v>7866</v>
       </c>
       <c r="G40" t="n">
-        <v>2.84</v>
+        <v>2.8385</v>
       </c>
       <c r="H40" t="n">
-        <v>47.08</v>
+        <v>47.078</v>
       </c>
       <c r="I40" t="n">
-        <v>46.78</v>
+        <v>46.785</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.29</v>
+        <v>-0.293</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>196432</v>
       </c>
       <c r="O40" t="n">
-        <v>70.22</v>
+        <v>70.2152</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -3572,16 +3572,16 @@
         <v>-2550</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.12</v>
+        <v>-1.1246</v>
       </c>
       <c r="H41" t="n">
-        <v>46.71</v>
+        <v>46.7123</v>
       </c>
       <c r="I41" t="n">
-        <v>46.83</v>
+        <v>46.8256</v>
       </c>
       <c r="J41" t="n">
-        <v>0.11</v>
+        <v>0.1133</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>176466</v>
       </c>
       <c r="O41" t="n">
-        <v>77.08</v>
+        <v>77.0752</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -3642,16 +3642,16 @@
         <v>-5268</v>
       </c>
       <c r="G42" t="n">
-        <v>-2.28</v>
+        <v>-2.2794</v>
       </c>
       <c r="H42" t="n">
-        <v>47.07</v>
+        <v>47.0672</v>
       </c>
       <c r="I42" t="n">
-        <v>47.27</v>
+        <v>47.2726</v>
       </c>
       <c r="J42" t="n">
-        <v>0.21</v>
+        <v>0.2054</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>177596</v>
       </c>
       <c r="O42" t="n">
-        <v>76.42</v>
+        <v>76.4179</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -3712,16 +3712,16 @@
         <v>-3620</v>
       </c>
       <c r="G43" t="n">
-        <v>-1.55</v>
+        <v>-1.5491</v>
       </c>
       <c r="H43" t="n">
-        <v>47.64</v>
+        <v>47.6374</v>
       </c>
       <c r="I43" t="n">
-        <v>47.52</v>
+        <v>47.5243</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.11</v>
+        <v>-0.1131</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>199030</v>
       </c>
       <c r="O43" t="n">
-        <v>84.81999999999999</v>
+        <v>84.8207</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -3782,16 +3782,16 @@
         <v>-4709</v>
       </c>
       <c r="G44" t="n">
-        <v>-1.87</v>
+        <v>-1.868</v>
       </c>
       <c r="H44" t="n">
-        <v>48.3</v>
+        <v>48.2988</v>
       </c>
       <c r="I44" t="n">
-        <v>48.28</v>
+        <v>48.2792</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.02</v>
+        <v>-0.0196</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>213563</v>
       </c>
       <c r="O44" t="n">
-        <v>84.42</v>
+        <v>84.4173</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -3852,16 +3852,16 @@
         <v>-132</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.05</v>
+        <v>-0.0504</v>
       </c>
       <c r="H45" t="n">
-        <v>48.09</v>
+        <v>48.0938</v>
       </c>
       <c r="I45" t="n">
-        <v>48.11</v>
+        <v>48.1085</v>
       </c>
       <c r="J45" t="n">
-        <v>0.01</v>
+        <v>0.0147</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>206004</v>
       </c>
       <c r="O45" t="n">
-        <v>78.45999999999999</v>
+        <v>78.46129999999999</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -3922,16 +3922,16 @@
         <v>639</v>
       </c>
       <c r="G46" t="n">
-        <v>0.25</v>
+        <v>0.2519</v>
       </c>
       <c r="H46" t="n">
-        <v>48.45</v>
+        <v>48.447</v>
       </c>
       <c r="I46" t="n">
-        <v>48.19</v>
+        <v>48.1947</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.25</v>
+        <v>-0.2523</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>201924</v>
       </c>
       <c r="O46" t="n">
-        <v>79.42</v>
+        <v>79.41849999999999</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -3992,16 +3992,16 @@
         <v>25240</v>
       </c>
       <c r="G47" t="n">
-        <v>5.9</v>
+        <v>5.8963</v>
       </c>
       <c r="H47" t="n">
-        <v>48.05</v>
+        <v>48.0472</v>
       </c>
       <c r="I47" t="n">
-        <v>48.09</v>
+        <v>48.0926</v>
       </c>
       <c r="J47" t="n">
-        <v>0.05</v>
+        <v>0.0455</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>309792</v>
       </c>
       <c r="O47" t="n">
-        <v>72.20999999999999</v>
+        <v>72.208</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -4062,16 +4062,16 @@
         <v>-3460</v>
       </c>
       <c r="G48" t="n">
-        <v>-1.2</v>
+        <v>-1.1966</v>
       </c>
       <c r="H48" t="n">
-        <v>47.74</v>
+        <v>47.7408</v>
       </c>
       <c r="I48" t="n">
-        <v>47.69</v>
+        <v>47.692</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.05</v>
+        <v>-0.0488</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>226724</v>
       </c>
       <c r="O48" t="n">
-        <v>78.28</v>
+        <v>78.2762</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -4132,16 +4132,16 @@
         <v>4010</v>
       </c>
       <c r="G49" t="n">
-        <v>1.73</v>
+        <v>1.7297</v>
       </c>
       <c r="H49" t="n">
-        <v>47.36</v>
+        <v>47.3615</v>
       </c>
       <c r="I49" t="n">
-        <v>47.07</v>
+        <v>47.0661</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.3</v>
+        <v>-0.2953</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>179709</v>
       </c>
       <c r="O49" t="n">
-        <v>77.39</v>
+        <v>77.3884</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -4202,16 +4202,16 @@
         <v>12490</v>
       </c>
       <c r="G50" t="n">
-        <v>4.91</v>
+        <v>4.9101</v>
       </c>
       <c r="H50" t="n">
-        <v>47.3</v>
+        <v>47.3022</v>
       </c>
       <c r="I50" t="n">
-        <v>47.78</v>
+        <v>47.7768</v>
       </c>
       <c r="J50" t="n">
-        <v>0.47</v>
+        <v>0.4746</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>195173</v>
       </c>
       <c r="O50" t="n">
-        <v>76.72</v>
+        <v>76.7165</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -4272,16 +4272,16 @@
         <v>28035</v>
       </c>
       <c r="G51" t="n">
-        <v>8.210000000000001</v>
+        <v>8.2058</v>
       </c>
       <c r="H51" t="n">
-        <v>47.99</v>
+        <v>47.9887</v>
       </c>
       <c r="I51" t="n">
-        <v>48.42</v>
+        <v>48.4184</v>
       </c>
       <c r="J51" t="n">
-        <v>0.43</v>
+        <v>0.4297</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>250409</v>
       </c>
       <c r="O51" t="n">
-        <v>73.15000000000001</v>
+        <v>73.1459</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
@@ -4342,16 +4342,16 @@
         <v>41422</v>
       </c>
       <c r="G52" t="n">
-        <v>16.88</v>
+        <v>16.877</v>
       </c>
       <c r="H52" t="n">
-        <v>48.47</v>
+        <v>48.4656</v>
       </c>
       <c r="I52" t="n">
-        <v>48.63</v>
+        <v>48.6339</v>
       </c>
       <c r="J52" t="n">
-        <v>0.17</v>
+        <v>0.1683</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>173451</v>
       </c>
       <c r="O52" t="n">
-        <v>70.64</v>
+        <v>70.63549999999999</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -4412,16 +4412,16 @@
         <v>17454</v>
       </c>
       <c r="G53" t="n">
-        <v>9.06</v>
+        <v>9.0604</v>
       </c>
       <c r="H53" t="n">
-        <v>47.71</v>
+        <v>47.7064</v>
       </c>
       <c r="I53" t="n">
-        <v>48.04</v>
+        <v>48.0441</v>
       </c>
       <c r="J53" t="n">
-        <v>0.34</v>
+        <v>0.3377</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>148869</v>
       </c>
       <c r="O53" t="n">
-        <v>77.27</v>
+        <v>77.2687</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
@@ -4482,16 +4482,16 @@
         <v>33132</v>
       </c>
       <c r="G54" t="n">
-        <v>12.35</v>
+        <v>12.3452</v>
       </c>
       <c r="H54" t="n">
-        <v>47.39</v>
+        <v>47.3914</v>
       </c>
       <c r="I54" t="n">
-        <v>47.66</v>
+        <v>47.6591</v>
       </c>
       <c r="J54" t="n">
-        <v>0.27</v>
+        <v>0.2677</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>198217</v>
       </c>
       <c r="O54" t="n">
-        <v>73.84999999999999</v>
+        <v>73.84610000000001</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -4552,16 +4552,16 @@
         <v>21814</v>
       </c>
       <c r="G55" t="n">
-        <v>10.06</v>
+        <v>10.0584</v>
       </c>
       <c r="H55" t="n">
-        <v>48.76</v>
+        <v>48.7603</v>
       </c>
       <c r="I55" t="n">
-        <v>49.34</v>
+        <v>49.343</v>
       </c>
       <c r="J55" t="n">
-        <v>0.58</v>
+        <v>0.5827</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>152606</v>
       </c>
       <c r="O55" t="n">
-        <v>70.33</v>
+        <v>70.3292</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -4622,16 +4622,16 @@
         <v>25282</v>
       </c>
       <c r="G56" t="n">
-        <v>7.22</v>
+        <v>7.2228</v>
       </c>
       <c r="H56" t="n">
-        <v>47.69</v>
+        <v>47.6899</v>
       </c>
       <c r="I56" t="n">
-        <v>48.2</v>
+        <v>48.1958</v>
       </c>
       <c r="J56" t="n">
-        <v>0.51</v>
+        <v>0.5059</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>248412</v>
       </c>
       <c r="O56" t="n">
-        <v>70.93000000000001</v>
+        <v>70.9252</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -4692,16 +4692,16 @@
         <v>10062</v>
       </c>
       <c r="G57" t="n">
-        <v>2.86</v>
+        <v>2.8551</v>
       </c>
       <c r="H57" t="n">
-        <v>47.58</v>
+        <v>47.583</v>
       </c>
       <c r="I57" t="n">
-        <v>47.78</v>
+        <v>47.7842</v>
       </c>
       <c r="J57" t="n">
-        <v>0.2</v>
+        <v>0.2012</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>256748</v>
       </c>
       <c r="O57" t="n">
-        <v>72.81</v>
+        <v>72.80929999999999</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
@@ -4762,16 +4762,16 @@
         <v>-3168</v>
       </c>
       <c r="G58" t="n">
-        <v>-1.35</v>
+        <v>-1.351</v>
       </c>
       <c r="H58" t="n">
-        <v>48.06</v>
+        <v>48.0592</v>
       </c>
       <c r="I58" t="n">
-        <v>48.18</v>
+        <v>48.1781</v>
       </c>
       <c r="J58" t="n">
-        <v>0.12</v>
+        <v>0.1189</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>185872</v>
       </c>
       <c r="O58" t="n">
-        <v>79.18000000000001</v>
+        <v>79.1794</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
@@ -4832,16 +4832,16 @@
         <v>-2093</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.91</v>
+        <v>-0.9062</v>
       </c>
       <c r="H59" t="n">
-        <v>47.88</v>
+        <v>47.8777</v>
       </c>
       <c r="I59" t="n">
-        <v>47.89</v>
+        <v>47.8905</v>
       </c>
       <c r="J59" t="n">
-        <v>0.01</v>
+        <v>0.0128</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>176557</v>
       </c>
       <c r="O59" t="n">
-        <v>76.40000000000001</v>
+        <v>76.4028</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -4902,16 +4902,16 @@
         <v>16708</v>
       </c>
       <c r="G60" t="n">
-        <v>6.39</v>
+        <v>6.3854</v>
       </c>
       <c r="H60" t="n">
-        <v>46.95</v>
+        <v>46.9522</v>
       </c>
       <c r="I60" t="n">
-        <v>46.42</v>
+        <v>46.4156</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.54</v>
+        <v>-0.5365</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>224795</v>
       </c>
       <c r="O60" t="n">
-        <v>85.56</v>
+        <v>85.5622</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
@@ -4972,16 +4972,16 @@
         <v>-2669</v>
       </c>
       <c r="G61" t="n">
-        <v>-1.05</v>
+        <v>-1.0487</v>
       </c>
       <c r="H61" t="n">
-        <v>47.57</v>
+        <v>47.5665</v>
       </c>
       <c r="I61" t="n">
-        <v>47.35</v>
+        <v>47.354</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.21</v>
+        <v>-0.2125</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>202089</v>
       </c>
       <c r="O61" t="n">
-        <v>78.7</v>
+        <v>78.7021</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
@@ -5042,16 +5042,16 @@
         <v>5160</v>
       </c>
       <c r="G62" t="n">
-        <v>2.17</v>
+        <v>2.1703</v>
       </c>
       <c r="H62" t="n">
-        <v>47.66</v>
+        <v>47.6606</v>
       </c>
       <c r="I62" t="n">
-        <v>47.19</v>
+        <v>47.1917</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.47</v>
+        <v>-0.4689</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>182838</v>
       </c>
       <c r="O62" t="n">
-        <v>75.67</v>
+        <v>75.6733</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -5112,16 +5112,16 @@
         <v>4500</v>
       </c>
       <c r="G63" t="n">
-        <v>1.94</v>
+        <v>1.9352</v>
       </c>
       <c r="H63" t="n">
-        <v>47.7</v>
+        <v>47.6986</v>
       </c>
       <c r="I63" t="n">
-        <v>47.06</v>
+        <v>47.0647</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.63</v>
+        <v>-0.6339</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>175866</v>
       </c>
       <c r="O63" t="n">
-        <v>74.11</v>
+        <v>74.1097</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -5182,16 +5182,16 @@
         <v>3389</v>
       </c>
       <c r="G64" t="n">
-        <v>1.34</v>
+        <v>1.3437</v>
       </c>
       <c r="H64" t="n">
-        <v>46.76</v>
+        <v>46.7645</v>
       </c>
       <c r="I64" t="n">
-        <v>46.76</v>
+        <v>46.7612</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>-0.0033</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>182026</v>
       </c>
       <c r="O64" t="n">
-        <v>71.45</v>
+        <v>71.452</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -5252,16 +5252,16 @@
         <v>-815</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.37</v>
+        <v>-0.3687</v>
       </c>
       <c r="H65" t="n">
-        <v>46.53</v>
+        <v>46.5319</v>
       </c>
       <c r="I65" t="n">
-        <v>46.54</v>
+        <v>46.5412</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01</v>
+        <v>0.0094</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>168807</v>
       </c>
       <c r="O65" t="n">
-        <v>76.17</v>
+        <v>76.173</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>-9039</v>
       </c>
       <c r="G66" t="n">
-        <v>-3.46</v>
+        <v>-3.4554</v>
       </c>
       <c r="H66" t="n">
-        <v>47.17</v>
+        <v>47.1662</v>
       </c>
       <c r="I66" t="n">
-        <v>47.11</v>
+        <v>47.1117</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.05</v>
+        <v>-0.0544</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>196680</v>
       </c>
       <c r="O66" t="n">
-        <v>74.87</v>
+        <v>74.87009999999999</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -5392,16 +5392,16 @@
         <v>24780</v>
       </c>
       <c r="G67" t="n">
-        <v>9.42</v>
+        <v>9.4186</v>
       </c>
       <c r="H67" t="n">
-        <v>47.96</v>
+        <v>47.9612</v>
       </c>
       <c r="I67" t="n">
-        <v>47.85</v>
+        <v>47.8541</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.11</v>
+        <v>-0.1071</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>175863</v>
       </c>
       <c r="O67" t="n">
-        <v>66.72</v>
+        <v>66.7197</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -5462,16 +5462,16 @@
         <v>-4307</v>
       </c>
       <c r="G68" t="n">
-        <v>-1.59</v>
+        <v>-1.5886</v>
       </c>
       <c r="H68" t="n">
-        <v>47.06</v>
+        <v>47.059</v>
       </c>
       <c r="I68" t="n">
-        <v>46.87</v>
+        <v>46.8721</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.19</v>
+        <v>-0.1869</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>211159</v>
       </c>
       <c r="O68" t="n">
-        <v>77.70999999999999</v>
+        <v>77.7051</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
@@ -5532,16 +5532,16 @@
         <v>808</v>
       </c>
       <c r="G69" t="n">
-        <v>0.31</v>
+        <v>0.3063</v>
       </c>
       <c r="H69" t="n">
-        <v>46.55</v>
+        <v>46.5476</v>
       </c>
       <c r="I69" t="n">
-        <v>46.49</v>
+        <v>46.4898</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.06</v>
+        <v>-0.0578</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>185998</v>
       </c>
       <c r="O69" t="n">
-        <v>70.23</v>
+        <v>70.2287</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
@@ -5602,16 +5602,16 @@
         <v>355</v>
       </c>
       <c r="G70" t="n">
-        <v>0.16</v>
+        <v>0.1557</v>
       </c>
       <c r="H70" t="n">
-        <v>46.5</v>
+        <v>46.5025</v>
       </c>
       <c r="I70" t="n">
-        <v>46.24</v>
+        <v>46.2351</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.27</v>
+        <v>-0.2675</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>164389</v>
       </c>
       <c r="O70" t="n">
-        <v>71.66</v>
+        <v>71.66070000000001</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -5672,16 +5672,16 @@
         <v>-7922</v>
       </c>
       <c r="G71" t="n">
-        <v>-2.98</v>
+        <v>-2.9843</v>
       </c>
       <c r="H71" t="n">
-        <v>46.53</v>
+        <v>46.5269</v>
       </c>
       <c r="I71" t="n">
-        <v>46.09</v>
+        <v>46.088</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.44</v>
+        <v>-0.4389</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
         <v>207982</v>
       </c>
       <c r="O71" t="n">
-        <v>78.25</v>
+        <v>78.2467</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
@@ -5742,16 +5742,16 @@
         <v>-3454</v>
       </c>
       <c r="G72" t="n">
-        <v>-1.39</v>
+        <v>-1.3881</v>
       </c>
       <c r="H72" t="n">
-        <v>46.65</v>
+        <v>46.6528</v>
       </c>
       <c r="I72" t="n">
-        <v>46.59</v>
+        <v>46.5896</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.06</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>201439</v>
       </c>
       <c r="O72" t="n">
-        <v>80.53</v>
+        <v>80.5279</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
@@ -5812,16 +5812,16 @@
         <v>5364</v>
       </c>
       <c r="G73" t="n">
-        <v>2.1</v>
+        <v>2.102</v>
       </c>
       <c r="H73" t="n">
-        <v>47.01</v>
+        <v>47.0147</v>
       </c>
       <c r="I73" t="n">
-        <v>46.57</v>
+        <v>46.5743</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.44</v>
+        <v>-0.4404</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>177818</v>
       </c>
       <c r="O73" t="n">
-        <v>69.05</v>
+        <v>69.0483</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
@@ -5882,16 +5882,16 @@
         <v>12148</v>
       </c>
       <c r="G74" t="n">
-        <v>4.37</v>
+        <v>4.3715</v>
       </c>
       <c r="H74" t="n">
-        <v>47.43</v>
+        <v>47.4326</v>
       </c>
       <c r="I74" t="n">
-        <v>46.93</v>
+        <v>46.9303</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.5</v>
+        <v>-0.5023</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>189277</v>
       </c>
       <c r="O74" t="n">
-        <v>67.83</v>
+        <v>67.8334</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -5952,16 +5952,16 @@
         <v>1157</v>
       </c>
       <c r="G75" t="n">
-        <v>0.4</v>
+        <v>0.3983</v>
       </c>
       <c r="H75" t="n">
-        <v>46.54</v>
+        <v>46.5358</v>
       </c>
       <c r="I75" t="n">
-        <v>46.03</v>
+        <v>46.0292</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.51</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6022,16 +6022,16 @@
         <v>1434</v>
       </c>
       <c r="G76" t="n">
-        <v>0.53</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>46.48</v>
+        <v>46.4837</v>
       </c>
       <c r="I76" t="n">
-        <v>45.88</v>
+        <v>45.8798</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.6</v>
+        <v>-0.604</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>188953</v>
       </c>
       <c r="O76" t="n">
-        <v>69.37</v>
+        <v>69.3719</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
@@ -6092,16 +6092,16 @@
         <v>849</v>
       </c>
       <c r="G77" t="n">
-        <v>0.32</v>
+        <v>0.3199</v>
       </c>
       <c r="H77" t="n">
-        <v>46.42</v>
+        <v>46.4242</v>
       </c>
       <c r="I77" t="n">
-        <v>45.91</v>
+        <v>45.9087</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.52</v>
+        <v>-0.5155</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>192495</v>
       </c>
       <c r="O77" t="n">
-        <v>72.23</v>
+        <v>72.2278</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
@@ -6162,16 +6162,16 @@
         <v>-5909</v>
       </c>
       <c r="G78" t="n">
-        <v>-2.91</v>
+        <v>-2.9116</v>
       </c>
       <c r="H78" t="n">
-        <v>45.59</v>
+        <v>45.586</v>
       </c>
       <c r="I78" t="n">
-        <v>45.7</v>
+        <v>45.6977</v>
       </c>
       <c r="J78" t="n">
-        <v>0.11</v>
+        <v>0.1117</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>151356</v>
       </c>
       <c r="O78" t="n">
-        <v>74.48</v>
+        <v>74.47629999999999</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
@@ -6232,16 +6232,16 @@
         <v>-4582</v>
       </c>
       <c r="G79" t="n">
-        <v>-1.93</v>
+        <v>-1.9323</v>
       </c>
       <c r="H79" t="n">
-        <v>46.29</v>
+        <v>46.2931</v>
       </c>
       <c r="I79" t="n">
-        <v>45.99</v>
+        <v>45.9886</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.3</v>
+        <v>-0.3046</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>201567</v>
       </c>
       <c r="O79" t="n">
-        <v>84.92</v>
+        <v>84.9222</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
@@ -6302,16 +6302,16 @@
         <v>2008</v>
       </c>
       <c r="G80" t="n">
-        <v>0.9</v>
+        <v>0.9001</v>
       </c>
       <c r="H80" t="n">
-        <v>46.84</v>
+        <v>46.8443</v>
       </c>
       <c r="I80" t="n">
-        <v>46.41</v>
+        <v>46.4099</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.43</v>
+        <v>-0.4344</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>174458</v>
       </c>
       <c r="O80" t="n">
-        <v>78.14</v>
+        <v>78.1401</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
@@ -6372,16 +6372,16 @@
         <v>1381</v>
       </c>
       <c r="G81" t="n">
-        <v>0.64</v>
+        <v>0.6438</v>
       </c>
       <c r="H81" t="n">
-        <v>46.17</v>
+        <v>46.1678</v>
       </c>
       <c r="I81" t="n">
-        <v>45.75</v>
+        <v>45.7463</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.42</v>
+        <v>-0.4215</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>167315</v>
       </c>
       <c r="O81" t="n">
-        <v>77.84999999999999</v>
+        <v>77.8488</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
@@ -6442,16 +6442,16 @@
         <v>4299</v>
       </c>
       <c r="G82" t="n">
-        <v>1.53</v>
+        <v>1.5343</v>
       </c>
       <c r="H82" t="n">
-        <v>45.9</v>
+        <v>45.9045</v>
       </c>
       <c r="I82" t="n">
-        <v>45.95</v>
+        <v>45.9539</v>
       </c>
       <c r="J82" t="n">
-        <v>0.05</v>
+        <v>0.0495</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>180079</v>
       </c>
       <c r="O82" t="n">
-        <v>63.94</v>
+        <v>63.9378</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
@@ -6512,16 +6512,16 @@
         <v>3558</v>
       </c>
       <c r="G83" t="n">
-        <v>1.29</v>
+        <v>1.2918</v>
       </c>
       <c r="H83" t="n">
-        <v>46.53</v>
+        <v>46.5312</v>
       </c>
       <c r="I83" t="n">
-        <v>46.17</v>
+        <v>46.1669</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.36</v>
+        <v>-0.3643</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>187418</v>
       </c>
       <c r="O83" t="n">
-        <v>67.68000000000001</v>
+        <v>67.6827</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -6582,16 +6582,16 @@
         <v>4587</v>
       </c>
       <c r="G84" t="n">
-        <v>1.79</v>
+        <v>1.7908</v>
       </c>
       <c r="H84" t="n">
-        <v>45.93</v>
+        <v>45.9301</v>
       </c>
       <c r="I84" t="n">
-        <v>45.68</v>
+        <v>45.676</v>
       </c>
       <c r="J84" t="n">
-        <v>-0.25</v>
+        <v>-0.2541</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>194894</v>
       </c>
       <c r="O84" t="n">
-        <v>75.86</v>
+        <v>75.85899999999999</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
@@ -6652,16 +6652,16 @@
         <v>-5632</v>
       </c>
       <c r="G85" t="n">
-        <v>-2.05</v>
+        <v>-2.0498</v>
       </c>
       <c r="H85" t="n">
-        <v>45.55</v>
+        <v>45.5499</v>
       </c>
       <c r="I85" t="n">
-        <v>45.69</v>
+        <v>45.6896</v>
       </c>
       <c r="J85" t="n">
-        <v>0.14</v>
+        <v>0.1397</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>198042</v>
       </c>
       <c r="O85" t="n">
-        <v>72.01000000000001</v>
+        <v>72.0142</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
@@ -6722,16 +6722,16 @@
         <v>64</v>
       </c>
       <c r="G86" t="n">
-        <v>0.03</v>
+        <v>0.0289</v>
       </c>
       <c r="H86" t="n">
-        <v>47.24</v>
+        <v>47.2382</v>
       </c>
       <c r="I86" t="n">
-        <v>46.93</v>
+        <v>46.9295</v>
       </c>
       <c r="J86" t="n">
-        <v>-0.31</v>
+        <v>-0.3087</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>179566</v>
       </c>
       <c r="O86" t="n">
-        <v>80.73999999999999</v>
+        <v>80.7445</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
@@ -6792,16 +6792,16 @@
         <v>2486</v>
       </c>
       <c r="G87" t="n">
-        <v>1.13</v>
+        <v>1.1289</v>
       </c>
       <c r="H87" t="n">
-        <v>46.49</v>
+        <v>46.491</v>
       </c>
       <c r="I87" t="n">
-        <v>46.09</v>
+        <v>46.0863</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.4</v>
+        <v>-0.4047</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>159798</v>
       </c>
       <c r="O87" t="n">
-        <v>72.20999999999999</v>
+        <v>72.2081</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
@@ -6862,16 +6862,16 @@
         <v>-2396</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.91</v>
+        <v>-0.9125</v>
       </c>
       <c r="H88" t="n">
-        <v>46.87</v>
+        <v>46.8665</v>
       </c>
       <c r="I88" t="n">
-        <v>46.72</v>
+        <v>46.7175</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.15</v>
+        <v>-0.149</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>183708</v>
       </c>
       <c r="O88" t="n">
-        <v>69.73999999999999</v>
+        <v>69.7441</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
@@ -6932,16 +6932,16 @@
         <v>12512</v>
       </c>
       <c r="G89" t="n">
-        <v>5.15</v>
+        <v>5.1471</v>
       </c>
       <c r="H89" t="n">
-        <v>47.3</v>
+        <v>47.3001</v>
       </c>
       <c r="I89" t="n">
-        <v>46.79</v>
+        <v>46.7884</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.51</v>
+        <v>-0.5117</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>182550</v>
       </c>
       <c r="O89" t="n">
-        <v>74.97</v>
+        <v>74.9744</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
@@ -7002,16 +7002,16 @@
         <v>632</v>
       </c>
       <c r="G90" t="n">
-        <v>0.25</v>
+        <v>0.2477</v>
       </c>
       <c r="H90" t="n">
-        <v>46.82</v>
+        <v>46.8166</v>
       </c>
       <c r="I90" t="n">
-        <v>46.57</v>
+        <v>46.5675</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.25</v>
+        <v>-0.2492</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>199062</v>
       </c>
       <c r="O90" t="n">
-        <v>77.98</v>
+        <v>77.98099999999999</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
@@ -7072,16 +7072,16 @@
         <v>12355</v>
       </c>
       <c r="G91" t="n">
-        <v>4.6</v>
+        <v>4.6045</v>
       </c>
       <c r="H91" t="n">
-        <v>46.58</v>
+        <v>46.5825</v>
       </c>
       <c r="I91" t="n">
-        <v>46.25</v>
+        <v>46.2458</v>
       </c>
       <c r="J91" t="n">
-        <v>-0.34</v>
+        <v>-0.3367</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>199355</v>
       </c>
       <c r="O91" t="n">
-        <v>74.22</v>
+        <v>74.21729999999999</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
@@ -7142,16 +7142,16 @@
         <v>1179</v>
       </c>
       <c r="G92" t="n">
-        <v>0.48</v>
+        <v>0.4846</v>
       </c>
       <c r="H92" t="n">
-        <v>46.19</v>
+        <v>46.1926</v>
       </c>
       <c r="I92" t="n">
-        <v>45.99</v>
+        <v>45.9851</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.21</v>
+        <v>-0.2075</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>158710</v>
       </c>
       <c r="O92" t="n">
-        <v>65.17</v>
+        <v>65.1717</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
@@ -7212,16 +7212,16 @@
         <v>11281</v>
       </c>
       <c r="G93" t="n">
-        <v>4.4</v>
+        <v>4.401</v>
       </c>
       <c r="H93" t="n">
-        <v>47.03</v>
+        <v>47.0317</v>
       </c>
       <c r="I93" t="n">
-        <v>46.64</v>
+        <v>46.639</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.39</v>
+        <v>-0.3927</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>184128</v>
       </c>
       <c r="O93" t="n">
-        <v>71.77</v>
+        <v>71.7694</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
@@ -7282,16 +7282,16 @@
         <v>-3687</v>
       </c>
       <c r="G94" t="n">
-        <v>-1.49</v>
+        <v>-1.4884</v>
       </c>
       <c r="H94" t="n">
-        <v>46.59</v>
+        <v>46.5928</v>
       </c>
       <c r="I94" t="n">
-        <v>46.67</v>
+        <v>46.6668</v>
       </c>
       <c r="J94" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>180253</v>
       </c>
       <c r="O94" t="n">
-        <v>72.73</v>
+        <v>72.7325</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
@@ -7352,16 +7352,16 @@
         <v>4390</v>
       </c>
       <c r="G95" t="n">
-        <v>1.62</v>
+        <v>1.6202</v>
       </c>
       <c r="H95" t="n">
-        <v>48.84</v>
+        <v>48.8411</v>
       </c>
       <c r="I95" t="n">
-        <v>48.44</v>
+        <v>48.4446</v>
       </c>
       <c r="J95" t="n">
-        <v>-0.4</v>
+        <v>-0.3965</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>208431</v>
       </c>
       <c r="O95" t="n">
-        <v>76.81</v>
+        <v>76.8103</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
@@ -7422,16 +7422,16 @@
         <v>7453</v>
       </c>
       <c r="G96" t="n">
-        <v>2.62</v>
+        <v>2.6184</v>
       </c>
       <c r="H96" t="n">
-        <v>48.45</v>
+        <v>48.4475</v>
       </c>
       <c r="I96" t="n">
-        <v>47.89</v>
+        <v>47.8857</v>
       </c>
       <c r="J96" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.5618</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>199385</v>
       </c>
       <c r="O96" t="n">
-        <v>69.95999999999999</v>
+        <v>69.9631</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
@@ -7492,16 +7492,16 @@
         <v>9963</v>
       </c>
       <c r="G97" t="n">
-        <v>3.94</v>
+        <v>3.9406</v>
       </c>
       <c r="H97" t="n">
-        <v>48.8</v>
+        <v>48.8012</v>
       </c>
       <c r="I97" t="n">
-        <v>48.02</v>
+        <v>48.0176</v>
       </c>
       <c r="J97" t="n">
-        <v>-0.78</v>
+        <v>-0.7835</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>188557</v>
       </c>
       <c r="O97" t="n">
-        <v>74.47</v>
+        <v>74.4716</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
@@ -7562,16 +7562,16 @@
         <v>2700</v>
       </c>
       <c r="G98" t="n">
-        <v>0.91</v>
+        <v>0.9097</v>
       </c>
       <c r="H98" t="n">
-        <v>48.3</v>
+        <v>48.3049</v>
       </c>
       <c r="I98" t="n">
-        <v>47.76</v>
+        <v>47.7602</v>
       </c>
       <c r="J98" t="n">
-        <v>-0.54</v>
+        <v>-0.5447</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>221109</v>
       </c>
       <c r="O98" t="n">
-        <v>74.37</v>
+        <v>74.3683</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
@@ -7632,16 +7632,16 @@
         <v>7651</v>
       </c>
       <c r="G99" t="n">
-        <v>2.71</v>
+        <v>2.7143</v>
       </c>
       <c r="H99" t="n">
-        <v>48.58</v>
+        <v>48.5793</v>
       </c>
       <c r="I99" t="n">
-        <v>48.45</v>
+        <v>48.4487</v>
       </c>
       <c r="J99" t="n">
-        <v>-0.13</v>
+        <v>-0.1306</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>216740</v>
       </c>
       <c r="O99" t="n">
-        <v>76.68000000000001</v>
+        <v>76.6801</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
@@ -7702,16 +7702,16 @@
         <v>7332</v>
       </c>
       <c r="G100" t="n">
-        <v>2.92</v>
+        <v>2.9187</v>
       </c>
       <c r="H100" t="n">
-        <v>48.79</v>
+        <v>48.7897</v>
       </c>
       <c r="I100" t="n">
-        <v>48.19</v>
+        <v>48.1874</v>
       </c>
       <c r="J100" t="n">
-        <v>-0.6</v>
+        <v>-0.6022</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>189622</v>
       </c>
       <c r="O100" t="n">
-        <v>75.25</v>
+        <v>75.2501</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
@@ -7772,16 +7772,16 @@
         <v>13174</v>
       </c>
       <c r="G101" t="n">
-        <v>6.29</v>
+        <v>6.2865</v>
       </c>
       <c r="H101" t="n">
-        <v>49.79</v>
+        <v>49.7886</v>
       </c>
       <c r="I101" t="n">
         <v>49.67</v>
       </c>
       <c r="J101" t="n">
-        <v>-0.12</v>
+        <v>-0.1186</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>143169</v>
       </c>
       <c r="O101" t="n">
-        <v>68.22</v>
+        <v>68.2205</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
@@ -7842,16 +7842,16 @@
         <v>24352</v>
       </c>
       <c r="G102" t="n">
-        <v>11.59</v>
+        <v>11.5929</v>
       </c>
       <c r="H102" t="n">
-        <v>50.01</v>
+        <v>50.0064</v>
       </c>
       <c r="I102" t="n">
-        <v>49.55</v>
+        <v>49.5463</v>
       </c>
       <c r="J102" t="n">
-        <v>-0.46</v>
+        <v>-0.4601</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>142004</v>
       </c>
       <c r="O102" t="n">
-        <v>67.53</v>
+        <v>67.5287</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
@@ -7912,16 +7912,16 @@
         <v>2002</v>
       </c>
       <c r="G103" t="n">
-        <v>0.86</v>
+        <v>0.8596</v>
       </c>
       <c r="H103" t="n">
-        <v>48.99</v>
+        <v>48.9912</v>
       </c>
       <c r="I103" t="n">
-        <v>48.58</v>
+        <v>48.5758</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.42</v>
+        <v>-0.4154</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>181330</v>
       </c>
       <c r="O103" t="n">
-        <v>77.72</v>
+        <v>77.71599999999999</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
@@ -7982,16 +7982,16 @@
         <v>2411</v>
       </c>
       <c r="G104" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9355</v>
       </c>
       <c r="H104" t="n">
-        <v>49.15</v>
+        <v>49.1528</v>
       </c>
       <c r="I104" t="n">
-        <v>48.92</v>
+        <v>48.9237</v>
       </c>
       <c r="J104" t="n">
-        <v>-0.23</v>
+        <v>-0.2291</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>181730</v>
       </c>
       <c r="O104" t="n">
-        <v>70.31999999999999</v>
+        <v>70.3197</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
@@ -8052,16 +8052,16 @@
         <v>2550</v>
       </c>
       <c r="G105" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="H105" t="n">
-        <v>49.01</v>
+        <v>49.0095</v>
       </c>
       <c r="I105" t="n">
-        <v>48.75</v>
+        <v>48.7462</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.26</v>
+        <v>-0.2634</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>200036</v>
       </c>
       <c r="O105" t="n">
-        <v>73.47</v>
+        <v>73.4659</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
@@ -8122,16 +8122,16 @@
         <v>10098</v>
       </c>
       <c r="G106" t="n">
-        <v>3.86</v>
+        <v>3.861</v>
       </c>
       <c r="H106" t="n">
-        <v>49.24</v>
+        <v>49.2429</v>
       </c>
       <c r="I106" t="n">
-        <v>48.64</v>
+        <v>48.6355</v>
       </c>
       <c r="J106" t="n">
-        <v>-0.61</v>
+        <v>-0.6075</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>200355</v>
       </c>
       <c r="O106" t="n">
-        <v>76.55</v>
+        <v>76.5453</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
@@ -8192,16 +8192,16 @@
         <v>4469</v>
       </c>
       <c r="G107" t="n">
-        <v>1.67</v>
+        <v>1.6693</v>
       </c>
       <c r="H107" t="n">
-        <v>48.69</v>
+        <v>48.6883</v>
       </c>
       <c r="I107" t="n">
-        <v>48.26</v>
+        <v>48.2621</v>
       </c>
       <c r="J107" t="n">
-        <v>-0.43</v>
+        <v>-0.4263</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>193740</v>
       </c>
       <c r="O107" t="n">
-        <v>71.95</v>
+        <v>71.9541</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
@@ -8262,16 +8262,16 @@
         <v>4816</v>
       </c>
       <c r="G108" t="n">
-        <v>1.82</v>
+        <v>1.823</v>
       </c>
       <c r="H108" t="n">
-        <v>48.44</v>
+        <v>48.4397</v>
       </c>
       <c r="I108" t="n">
-        <v>48</v>
+        <v>47.9971</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.44</v>
+        <v>-0.4427</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>195933</v>
       </c>
       <c r="O108" t="n">
-        <v>73.7</v>
+        <v>73.6961</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -8332,16 +8332,16 @@
         <v>-1748</v>
       </c>
       <c r="G109" t="n">
-        <v>-0.67</v>
+        <v>-0.6687</v>
       </c>
       <c r="H109" t="n">
-        <v>48.34</v>
+        <v>48.3444</v>
       </c>
       <c r="I109" t="n">
-        <v>47.99</v>
+        <v>47.9906</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.35</v>
+        <v>-0.3538</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>179783</v>
       </c>
       <c r="O109" t="n">
-        <v>68.52</v>
+        <v>68.5151</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
@@ -8402,16 +8402,16 @@
         <v>11017</v>
       </c>
       <c r="G110" t="n">
-        <v>4.08</v>
+        <v>4.0756</v>
       </c>
       <c r="H110" t="n">
-        <v>48.23</v>
+        <v>48.2288</v>
       </c>
       <c r="I110" t="n">
-        <v>47.67</v>
+        <v>47.6701</v>
       </c>
       <c r="J110" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.5587</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>188186</v>
       </c>
       <c r="O110" t="n">
-        <v>69.51000000000001</v>
+        <v>69.5108</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
@@ -8472,16 +8472,16 @@
         <v>-1338</v>
       </c>
       <c r="G111" t="n">
-        <v>-0.47</v>
+        <v>-0.4737</v>
       </c>
       <c r="H111" t="n">
-        <v>47.74</v>
+        <v>47.7389</v>
       </c>
       <c r="I111" t="n">
-        <v>47.44</v>
+        <v>47.4366</v>
       </c>
       <c r="J111" t="n">
-        <v>-0.3</v>
+        <v>-0.3023</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>209361</v>
       </c>
       <c r="O111" t="n">
-        <v>73.97</v>
+        <v>73.96559999999999</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
@@ -8542,16 +8542,16 @@
         <v>8597</v>
       </c>
       <c r="G112" t="n">
-        <v>3.01</v>
+        <v>3.0057</v>
       </c>
       <c r="H112" t="n">
-        <v>48.3</v>
+        <v>48.296</v>
       </c>
       <c r="I112" t="n">
-        <v>47.97</v>
+        <v>47.9741</v>
       </c>
       <c r="J112" t="n">
-        <v>-0.32</v>
+        <v>-0.3219</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>202030</v>
       </c>
       <c r="O112" t="n">
-        <v>70.45</v>
+        <v>70.4526</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -8612,16 +8612,16 @@
         <v>4971</v>
       </c>
       <c r="G113" t="n">
-        <v>1.88</v>
+        <v>1.8764</v>
       </c>
       <c r="H113" t="n">
-        <v>48.48</v>
+        <v>48.4824</v>
       </c>
       <c r="I113" t="n">
-        <v>48.19</v>
+        <v>48.1896</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.29</v>
+        <v>-0.2927</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>191985</v>
       </c>
       <c r="O113" t="n">
-        <v>72.22</v>
+        <v>72.21850000000001</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
@@ -8682,16 +8682,16 @@
         <v>2517</v>
       </c>
       <c r="G114" t="n">
-        <v>0.93</v>
+        <v>0.9298</v>
       </c>
       <c r="H114" t="n">
-        <v>48.07</v>
+        <v>48.0737</v>
       </c>
       <c r="I114" t="n">
-        <v>47.74</v>
+        <v>47.7414</v>
       </c>
       <c r="J114" t="n">
-        <v>-0.33</v>
+        <v>-0.3322</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>205818</v>
       </c>
       <c r="O114" t="n">
-        <v>75.70999999999999</v>
+        <v>75.70569999999999</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
@@ -8752,16 +8752,16 @@
         <v>5252</v>
       </c>
       <c r="G115" t="n">
-        <v>2.11</v>
+        <v>2.1071</v>
       </c>
       <c r="H115" t="n">
-        <v>47.97</v>
+        <v>47.9744</v>
       </c>
       <c r="I115" t="n">
-        <v>47.65</v>
+        <v>47.6455</v>
       </c>
       <c r="J115" t="n">
-        <v>-0.33</v>
+        <v>-0.3288</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>196771</v>
       </c>
       <c r="O115" t="n">
-        <v>78.56999999999999</v>
+        <v>78.5723</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
@@ -8822,16 +8822,16 @@
         <v>3948</v>
       </c>
       <c r="G116" t="n">
-        <v>1.47</v>
+        <v>1.4743</v>
       </c>
       <c r="H116" t="n">
-        <v>48.58</v>
+        <v>48.5819</v>
       </c>
       <c r="I116" t="n">
-        <v>48.3</v>
+        <v>48.3029</v>
       </c>
       <c r="J116" t="n">
-        <v>-0.28</v>
+        <v>-0.279</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>202101</v>
       </c>
       <c r="O116" t="n">
-        <v>75.09999999999999</v>
+        <v>75.1045</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
@@ -8892,16 +8892,16 @@
         <v>6095</v>
       </c>
       <c r="G117" t="n">
-        <v>1.98</v>
+        <v>1.9766</v>
       </c>
       <c r="H117" t="n">
-        <v>48.27</v>
+        <v>48.2736</v>
       </c>
       <c r="I117" t="n">
-        <v>47.83</v>
+        <v>47.829</v>
       </c>
       <c r="J117" t="n">
-        <v>-0.44</v>
+        <v>-0.4446</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>213467</v>
       </c>
       <c r="O117" t="n">
-        <v>69.09999999999999</v>
+        <v>69.0968</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
@@ -8962,16 +8962,16 @@
         <v>4131</v>
       </c>
       <c r="G118" t="n">
-        <v>1.68</v>
+        <v>1.6791</v>
       </c>
       <c r="H118" t="n">
-        <v>48.79</v>
+        <v>48.7906</v>
       </c>
       <c r="I118" t="n">
-        <v>48.54</v>
+        <v>48.5436</v>
       </c>
       <c r="J118" t="n">
-        <v>-0.25</v>
+        <v>-0.247</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>170105</v>
       </c>
       <c r="O118" t="n">
-        <v>69.08</v>
+        <v>69.08150000000001</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
@@ -9032,16 +9032,16 @@
         <v>16820</v>
       </c>
       <c r="G119" t="n">
-        <v>6.13</v>
+        <v>6.1283</v>
       </c>
       <c r="H119" t="n">
-        <v>48.43</v>
+        <v>48.426</v>
       </c>
       <c r="I119" t="n">
-        <v>47.99</v>
+        <v>47.9899</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.44</v>
+        <v>-0.4362</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>189256</v>
       </c>
       <c r="O119" t="n">
-        <v>68.91</v>
+        <v>68.9058</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Marwar Junciton</t>
+          <t>Marwar Junction</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -9102,16 +9102,16 @@
         <v>8768</v>
       </c>
       <c r="G120" t="n">
-        <v>2.97</v>
+        <v>2.9738</v>
       </c>
       <c r="H120" t="n">
-        <v>47.85</v>
+        <v>47.8485</v>
       </c>
       <c r="I120" t="n">
-        <v>47.35</v>
+        <v>47.3484</v>
       </c>
       <c r="J120" t="n">
-        <v>-0.5</v>
+        <v>-0.5001</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>182293</v>
       </c>
       <c r="O120" t="n">
-        <v>61.8</v>
+        <v>61.8028</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
@@ -9172,16 +9172,16 @@
         <v>3252</v>
       </c>
       <c r="G121" t="n">
-        <v>0.98</v>
+        <v>0.9774</v>
       </c>
       <c r="H121" t="n">
-        <v>47.9</v>
+        <v>47.898</v>
       </c>
       <c r="I121" t="n">
-        <v>47.71</v>
+        <v>47.7121</v>
       </c>
       <c r="J121" t="n">
-        <v>-0.19</v>
+        <v>-0.1859</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>222020</v>
       </c>
       <c r="O121" t="n">
-        <v>66.70999999999999</v>
+        <v>66.7067</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
@@ -9242,16 +9242,16 @@
         <v>11049</v>
       </c>
       <c r="G122" t="n">
-        <v>3.55</v>
+        <v>3.5514</v>
       </c>
       <c r="H122" t="n">
-        <v>47.81</v>
+        <v>47.8111</v>
       </c>
       <c r="I122" t="n">
-        <v>47.27</v>
+        <v>47.2691</v>
       </c>
       <c r="J122" t="n">
-        <v>-0.54</v>
+        <v>-0.542</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>192486</v>
       </c>
       <c r="O122" t="n">
-        <v>61.85</v>
+        <v>61.8518</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -9312,16 +9312,16 @@
         <v>-3109</v>
       </c>
       <c r="G123" t="n">
-        <v>-1.21</v>
+        <v>-1.2112</v>
       </c>
       <c r="H123" t="n">
-        <v>46.63</v>
+        <v>46.6293</v>
       </c>
       <c r="I123" t="n">
-        <v>46.59</v>
+        <v>46.5898</v>
       </c>
       <c r="J123" t="n">
-        <v>-0.04</v>
+        <v>-0.0395</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>178528</v>
       </c>
       <c r="O123" t="n">
-        <v>69.33</v>
+        <v>69.3334</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
@@ -9382,16 +9382,16 @@
         <v>-10683</v>
       </c>
       <c r="G124" t="n">
-        <v>-4</v>
+        <v>-4.0023</v>
       </c>
       <c r="H124" t="n">
-        <v>46.63</v>
+        <v>46.6297</v>
       </c>
       <c r="I124" t="n">
-        <v>46.93</v>
+        <v>46.9296</v>
       </c>
       <c r="J124" t="n">
-        <v>0.3</v>
+        <v>0.2999</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>208488</v>
       </c>
       <c r="O124" t="n">
-        <v>77.72</v>
+        <v>77.7244</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
@@ -9452,16 +9452,16 @@
         <v>-4121</v>
       </c>
       <c r="G125" t="n">
-        <v>-1.5</v>
+        <v>-1.5008</v>
       </c>
       <c r="H125" t="n">
-        <v>47.03</v>
+        <v>47.0259</v>
       </c>
       <c r="I125" t="n">
-        <v>47.01</v>
+        <v>47.0133</v>
       </c>
       <c r="J125" t="n">
-        <v>-0.01</v>
+        <v>-0.0125</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>207127</v>
       </c>
       <c r="O125" t="n">
-        <v>75.08</v>
+        <v>75.08029999999999</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
@@ -9522,16 +9522,16 @@
         <v>-3321</v>
       </c>
       <c r="G126" t="n">
-        <v>-1.25</v>
+        <v>-1.2525</v>
       </c>
       <c r="H126" t="n">
-        <v>47.25</v>
+        <v>47.2542</v>
       </c>
       <c r="I126" t="n">
-        <v>47.21</v>
+        <v>47.2139</v>
       </c>
       <c r="J126" t="n">
-        <v>-0.04</v>
+        <v>-0.0403</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>209762</v>
       </c>
       <c r="O126" t="n">
-        <v>78.78</v>
+        <v>78.77849999999999</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
@@ -9592,16 +9592,16 @@
         <v>1257</v>
       </c>
       <c r="G127" t="n">
-        <v>0.41</v>
+        <v>0.4149</v>
       </c>
       <c r="H127" t="n">
-        <v>47.66</v>
+        <v>47.6604</v>
       </c>
       <c r="I127" t="n">
-        <v>47.51</v>
+        <v>47.5057</v>
       </c>
       <c r="J127" t="n">
-        <v>-0.15</v>
+        <v>-0.1547</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>202729</v>
       </c>
       <c r="O127" t="n">
-        <v>66.42</v>
+        <v>66.4247</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
@@ -9662,16 +9662,16 @@
         <v>38688</v>
       </c>
       <c r="G128" t="n">
-        <v>15.04</v>
+        <v>15.0425</v>
       </c>
       <c r="H128" t="n">
-        <v>49.01</v>
+        <v>49.0142</v>
       </c>
       <c r="I128" t="n">
-        <v>49.31</v>
+        <v>49.3124</v>
       </c>
       <c r="J128" t="n">
-        <v>0.3</v>
+        <v>0.2982</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>170910</v>
       </c>
       <c r="O128" t="n">
-        <v>66.3</v>
+        <v>66.3028</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
@@ -9732,16 +9732,16 @@
         <v>34714</v>
       </c>
       <c r="G129" t="n">
-        <v>17.39</v>
+        <v>17.3938</v>
       </c>
       <c r="H129" t="n">
-        <v>49.53</v>
+        <v>49.5283</v>
       </c>
       <c r="I129" t="n">
-        <v>49.25</v>
+        <v>49.2524</v>
       </c>
       <c r="J129" t="n">
-        <v>-0.28</v>
+        <v>-0.2758</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>132010</v>
       </c>
       <c r="O129" t="n">
-        <v>66.09999999999999</v>
+        <v>66.09950000000001</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
@@ -9802,16 +9802,16 @@
         <v>29656</v>
       </c>
       <c r="G130" t="n">
-        <v>10.28</v>
+        <v>10.2769</v>
       </c>
       <c r="H130" t="n">
-        <v>48.31</v>
+        <v>48.3056</v>
       </c>
       <c r="I130" t="n">
-        <v>48.67</v>
+        <v>48.6654</v>
       </c>
       <c r="J130" t="n">
-        <v>0.36</v>
+        <v>0.3598</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>200909</v>
       </c>
       <c r="O130" t="n">
-        <v>69.59999999999999</v>
+        <v>69.596</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
@@ -9872,16 +9872,16 @@
         <v>13029</v>
       </c>
       <c r="G131" t="n">
-        <v>3.89</v>
+        <v>3.8937</v>
       </c>
       <c r="H131" t="n">
-        <v>47.5</v>
+        <v>47.5021</v>
       </c>
       <c r="I131" t="n">
-        <v>47.39</v>
+        <v>47.3877</v>
       </c>
       <c r="J131" t="n">
-        <v>-0.11</v>
+        <v>-0.1144</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>244113</v>
       </c>
       <c r="O131" t="n">
-        <v>72.83</v>
+        <v>72.83280000000001</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
@@ -9942,16 +9942,16 @@
         <v>4198</v>
       </c>
       <c r="G132" t="n">
-        <v>1.45</v>
+        <v>1.4506</v>
       </c>
       <c r="H132" t="n">
-        <v>48.31</v>
+        <v>48.3103</v>
       </c>
       <c r="I132" t="n">
-        <v>47.92</v>
+        <v>47.9193</v>
       </c>
       <c r="J132" t="n">
-        <v>-0.39</v>
+        <v>-0.3909</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>196248</v>
       </c>
       <c r="O132" t="n">
-        <v>67.58</v>
+        <v>67.57640000000001</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
@@ -10012,16 +10012,16 @@
         <v>-5528</v>
       </c>
       <c r="G133" t="n">
-        <v>-2.19</v>
+        <v>-2.188</v>
       </c>
       <c r="H133" t="n">
-        <v>45.89</v>
+        <v>45.893</v>
       </c>
       <c r="I133" t="n">
-        <v>45.69</v>
+        <v>45.6932</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.2</v>
+        <v>-0.1998</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>198839</v>
       </c>
       <c r="O133" t="n">
-        <v>78.45999999999999</v>
+        <v>78.4629</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
@@ -10082,16 +10082,16 @@
         <v>1003</v>
       </c>
       <c r="G134" t="n">
-        <v>0.45</v>
+        <v>0.448</v>
       </c>
       <c r="H134" t="n">
-        <v>46.83</v>
+        <v>46.8267</v>
       </c>
       <c r="I134" t="n">
-        <v>46.5</v>
+        <v>46.5048</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.32</v>
+        <v>-0.3218</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>198794</v>
       </c>
       <c r="O134" t="n">
-        <v>88.48</v>
+        <v>88.4846</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
@@ -10152,16 +10152,16 @@
         <v>-14808</v>
       </c>
       <c r="G135" t="n">
-        <v>-4.93</v>
+        <v>-4.9288</v>
       </c>
       <c r="H135" t="n">
-        <v>45.73</v>
+        <v>45.7318</v>
       </c>
       <c r="I135" t="n">
-        <v>46.07</v>
+        <v>46.0655</v>
       </c>
       <c r="J135" t="n">
-        <v>0.33</v>
+        <v>0.3337</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>252882</v>
       </c>
       <c r="O135" t="n">
-        <v>84.06</v>
+        <v>84.0578</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
@@ -10222,16 +10222,16 @@
         <v>-1138</v>
       </c>
       <c r="G136" t="n">
-        <v>-0.43</v>
+        <v>-0.4302</v>
       </c>
       <c r="H136" t="n">
-        <v>47.01</v>
+        <v>47.0077</v>
       </c>
       <c r="I136" t="n">
-        <v>46.9</v>
+        <v>46.9038</v>
       </c>
       <c r="J136" t="n">
-        <v>-0.1</v>
+        <v>-0.1039</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>216916</v>
       </c>
       <c r="O136" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8974</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
@@ -10292,16 +10292,16 @@
         <v>-9810</v>
       </c>
       <c r="G137" t="n">
-        <v>-3.89</v>
+        <v>-3.8897</v>
       </c>
       <c r="H137" t="n">
-        <v>46.75</v>
+        <v>46.7502</v>
       </c>
       <c r="I137" t="n">
-        <v>46.85</v>
+        <v>46.8494</v>
       </c>
       <c r="J137" t="n">
-        <v>0.1</v>
+        <v>0.0992</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>213370</v>
       </c>
       <c r="O137" t="n">
-        <v>84.54000000000001</v>
+        <v>84.5361</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
@@ -10362,16 +10362,16 @@
         <v>2417</v>
       </c>
       <c r="G138" t="n">
-        <v>0.96</v>
+        <v>0.9565</v>
       </c>
       <c r="H138" t="n">
-        <v>47.39</v>
+        <v>47.3937</v>
       </c>
       <c r="I138" t="n">
-        <v>47.3</v>
+        <v>47.3028</v>
       </c>
       <c r="J138" t="n">
-        <v>-0.09</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>186620</v>
       </c>
       <c r="O138" t="n">
-        <v>73.78</v>
+        <v>73.7754</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
@@ -10432,16 +10432,16 @@
         <v>5594</v>
       </c>
       <c r="G139" t="n">
-        <v>2.03</v>
+        <v>2.0256</v>
       </c>
       <c r="H139" t="n">
-        <v>46.91</v>
+        <v>46.9117</v>
       </c>
       <c r="I139" t="n">
-        <v>46.81</v>
+        <v>46.8079</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.1</v>
+        <v>-0.1038</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>178703</v>
       </c>
       <c r="O139" t="n">
-        <v>64.69</v>
+        <v>64.68859999999999</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
@@ -10502,16 +10502,16 @@
         <v>-14391</v>
       </c>
       <c r="G140" t="n">
-        <v>-5.33</v>
+        <v>-5.3304</v>
       </c>
       <c r="H140" t="n">
-        <v>46.77</v>
+        <v>46.7677</v>
       </c>
       <c r="I140" t="n">
-        <v>47.27</v>
+        <v>47.2655</v>
       </c>
       <c r="J140" t="n">
-        <v>0.5</v>
+        <v>0.4978</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>220316</v>
       </c>
       <c r="O140" t="n">
-        <v>81.56</v>
+        <v>81.55800000000001</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
@@ -10572,16 +10572,16 @@
         <v>-11360</v>
       </c>
       <c r="G141" t="n">
-        <v>-3.67</v>
+        <v>-3.6699</v>
       </c>
       <c r="H141" t="n">
-        <v>46.47</v>
+        <v>46.4716</v>
       </c>
       <c r="I141" t="n">
-        <v>46.94</v>
+        <v>46.9439</v>
       </c>
       <c r="J141" t="n">
-        <v>0.47</v>
+        <v>0.4724</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>237451</v>
       </c>
       <c r="O141" t="n">
-        <v>76.66</v>
+        <v>76.6604</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
@@ -10642,16 +10642,16 @@
         <v>10688</v>
       </c>
       <c r="G142" t="n">
-        <v>3.94</v>
+        <v>3.9382</v>
       </c>
       <c r="H142" t="n">
-        <v>47.46</v>
+        <v>47.4572</v>
       </c>
       <c r="I142" t="n">
-        <v>46.99</v>
+        <v>46.992</v>
       </c>
       <c r="J142" t="n">
-        <v>-0.47</v>
+        <v>-0.4652</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>167769</v>
       </c>
       <c r="O142" t="n">
-        <v>61.8</v>
+        <v>61.8036</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
@@ -10712,16 +10712,16 @@
         <v>-2093</v>
       </c>
       <c r="G143" t="n">
-        <v>-0.73</v>
+        <v>-0.7269</v>
       </c>
       <c r="H143" t="n">
-        <v>47.06</v>
+        <v>47.0577</v>
       </c>
       <c r="I143" t="n">
-        <v>47.01</v>
+        <v>47.0057</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.05</v>
+        <v>-0.052</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>182096</v>
       </c>
       <c r="O143" t="n">
-        <v>63.24</v>
+        <v>63.2374</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
@@ -10782,16 +10782,16 @@
         <v>1202</v>
       </c>
       <c r="G144" t="n">
-        <v>0.39</v>
+        <v>0.3892</v>
       </c>
       <c r="H144" t="n">
-        <v>47.07</v>
+        <v>47.0748</v>
       </c>
       <c r="I144" t="n">
-        <v>46.89</v>
+        <v>46.8918</v>
       </c>
       <c r="J144" t="n">
-        <v>-0.18</v>
+        <v>-0.1831</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>203320</v>
       </c>
       <c r="O144" t="n">
-        <v>65.83</v>
+        <v>65.82940000000001</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
@@ -10852,16 +10852,16 @@
         <v>4232</v>
       </c>
       <c r="G145" t="n">
-        <v>1.34</v>
+        <v>1.3424</v>
       </c>
       <c r="H145" t="n">
-        <v>47.01</v>
+        <v>47.0087</v>
       </c>
       <c r="I145" t="n">
-        <v>46.6</v>
+        <v>46.5988</v>
       </c>
       <c r="J145" t="n">
-        <v>-0.41</v>
+        <v>-0.4098</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>257977</v>
       </c>
       <c r="O145" t="n">
-        <v>81.81</v>
+        <v>81.8146</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
@@ -10922,16 +10922,16 @@
         <v>-2075</v>
       </c>
       <c r="G146" t="n">
-        <v>-0.76</v>
+        <v>-0.7633</v>
       </c>
       <c r="H146" t="n">
-        <v>47.36</v>
+        <v>47.3615</v>
       </c>
       <c r="I146" t="n">
-        <v>47.15</v>
+        <v>47.1527</v>
       </c>
       <c r="J146" t="n">
-        <v>-0.21</v>
+        <v>-0.2087</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>213585</v>
       </c>
       <c r="O146" t="n">
-        <v>78.56</v>
+        <v>78.5603</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
@@ -10992,16 +10992,16 @@
         <v>17903</v>
       </c>
       <c r="G147" t="n">
-        <v>5.88</v>
+        <v>5.881</v>
       </c>
       <c r="H147" t="n">
-        <v>48.06</v>
+        <v>48.0629</v>
       </c>
       <c r="I147" t="n">
-        <v>47.65</v>
+        <v>47.6548</v>
       </c>
       <c r="J147" t="n">
-        <v>-0.41</v>
+        <v>-0.4081</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>202572</v>
       </c>
       <c r="O147" t="n">
-        <v>66.53</v>
+        <v>66.5279</v>
       </c>
       <c r="P147" t="inlineStr">
         <is>
@@ -11062,16 +11062,16 @@
         <v>4605</v>
       </c>
       <c r="G148" t="n">
-        <v>2.02</v>
+        <v>2.0172</v>
       </c>
       <c r="H148" t="n">
-        <v>48.33</v>
+        <v>48.3266</v>
       </c>
       <c r="I148" t="n">
         <v>48.19</v>
       </c>
       <c r="J148" t="n">
-        <v>-0.14</v>
+        <v>-0.1366</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>161224</v>
       </c>
       <c r="O148" t="n">
-        <v>70.61</v>
+        <v>70.6092</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
@@ -11132,16 +11132,16 @@
         <v>4672</v>
       </c>
       <c r="G149" t="n">
-        <v>1.65</v>
+        <v>1.6477</v>
       </c>
       <c r="H149" t="n">
-        <v>47.22</v>
+        <v>47.2215</v>
       </c>
       <c r="I149" t="n">
-        <v>47.13</v>
+        <v>47.129</v>
       </c>
       <c r="J149" t="n">
-        <v>-0.09</v>
+        <v>-0.0924</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>198385</v>
       </c>
       <c r="O149" t="n">
-        <v>69.95999999999999</v>
+        <v>69.9563</v>
       </c>
       <c r="P149" t="inlineStr">
         <is>
@@ -11202,16 +11202,16 @@
         <v>9203</v>
       </c>
       <c r="G150" t="n">
-        <v>3.48</v>
+        <v>3.4756</v>
       </c>
       <c r="H150" t="n">
-        <v>48.81</v>
+        <v>48.8072</v>
       </c>
       <c r="I150" t="n">
-        <v>47.85</v>
+        <v>47.8516</v>
       </c>
       <c r="J150" t="n">
-        <v>-0.96</v>
+        <v>-0.9556</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>196997</v>
       </c>
       <c r="O150" t="n">
-        <v>74.39</v>
+        <v>74.3918</v>
       </c>
       <c r="P150" t="inlineStr">
         <is>
@@ -11272,16 +11272,16 @@
         <v>-3214</v>
       </c>
       <c r="G151" t="n">
-        <v>-1.18</v>
+        <v>-1.1752</v>
       </c>
       <c r="H151" t="n">
-        <v>48.6</v>
+        <v>48.5999</v>
       </c>
       <c r="I151" t="n">
-        <v>47.6</v>
+        <v>47.6042</v>
       </c>
       <c r="J151" t="n">
-        <v>-1</v>
+        <v>-0.9957</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>218746</v>
       </c>
       <c r="O151" t="n">
-        <v>79.98</v>
+        <v>79.9811</v>
       </c>
       <c r="P151" t="inlineStr">
         <is>
@@ -11342,16 +11342,16 @@
         <v>6402</v>
       </c>
       <c r="G152" t="n">
-        <v>2.15</v>
+        <v>2.1512</v>
       </c>
       <c r="H152" t="n">
-        <v>49.02</v>
+        <v>49.0229</v>
       </c>
       <c r="I152" t="n">
-        <v>47.91</v>
+        <v>47.9149</v>
       </c>
       <c r="J152" t="n">
-        <v>-1.11</v>
+        <v>-1.108</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>219178</v>
       </c>
       <c r="O152" t="n">
-        <v>73.62</v>
+        <v>73.62130000000001</v>
       </c>
       <c r="P152" t="inlineStr">
         <is>
@@ -11412,16 +11412,16 @@
         <v>22589</v>
       </c>
       <c r="G153" t="n">
-        <v>7.92</v>
+        <v>7.9212</v>
       </c>
       <c r="H153" t="n">
-        <v>49.48</v>
+        <v>49.4849</v>
       </c>
       <c r="I153" t="n">
-        <v>49.07</v>
+        <v>49.0687</v>
       </c>
       <c r="J153" t="n">
-        <v>-0.42</v>
+        <v>-0.4162</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>214545</v>
       </c>
       <c r="O153" t="n">
-        <v>75.22</v>
+        <v>75.2225</v>
       </c>
       <c r="P153" t="inlineStr">
         <is>
@@ -11482,16 +11482,16 @@
         <v>31831</v>
       </c>
       <c r="G154" t="n">
-        <v>12.92</v>
+        <v>12.9201</v>
       </c>
       <c r="H154" t="n">
-        <v>49.76</v>
+        <v>49.7559</v>
       </c>
       <c r="I154" t="n">
-        <v>49.74</v>
+        <v>49.7385</v>
       </c>
       <c r="J154" t="n">
-        <v>-0.02</v>
+        <v>-0.0173</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>165949</v>
       </c>
       <c r="O154" t="n">
-        <v>67.34999999999999</v>
+        <v>67.3467</v>
       </c>
       <c r="P154" t="inlineStr">
         <is>
@@ -11552,16 +11552,16 @@
         <v>8489</v>
       </c>
       <c r="G155" t="n">
-        <v>3.29</v>
+        <v>3.2903</v>
       </c>
       <c r="H155" t="n">
-        <v>49.42</v>
+        <v>49.4153</v>
       </c>
       <c r="I155" t="n">
-        <v>48.88</v>
+        <v>48.883</v>
       </c>
       <c r="J155" t="n">
-        <v>-0.53</v>
+        <v>-0.5323</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>203460</v>
       </c>
       <c r="O155" t="n">
-        <v>78.84</v>
+        <v>78.84059999999999</v>
       </c>
       <c r="P155" t="inlineStr">
         <is>
@@ -11622,16 +11622,16 @@
         <v>10664</v>
       </c>
       <c r="G156" t="n">
-        <v>4.03</v>
+        <v>4.0288</v>
       </c>
       <c r="H156" t="n">
-        <v>49.13</v>
+        <v>49.1262</v>
       </c>
       <c r="I156" t="n">
-        <v>48.46</v>
+        <v>48.4644</v>
       </c>
       <c r="J156" t="n">
-        <v>-0.66</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>203903</v>
       </c>
       <c r="O156" t="n">
-        <v>77.01000000000001</v>
+        <v>77.0085</v>
       </c>
       <c r="P156" t="inlineStr">
         <is>
@@ -11692,16 +11692,16 @@
         <v>16774</v>
       </c>
       <c r="G157" t="n">
-        <v>5.68</v>
+        <v>5.6832</v>
       </c>
       <c r="H157" t="n">
-        <v>49.09</v>
+        <v>49.0884</v>
       </c>
       <c r="I157" t="n">
-        <v>48.26</v>
+        <v>48.2604</v>
       </c>
       <c r="J157" t="n">
-        <v>-0.83</v>
+        <v>-0.828</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>213319</v>
       </c>
       <c r="O157" t="n">
-        <v>72.27</v>
+        <v>72.26909999999999</v>
       </c>
       <c r="P157" t="inlineStr">
         <is>
@@ -11762,16 +11762,16 @@
         <v>4768</v>
       </c>
       <c r="G158" t="n">
-        <v>1.74</v>
+        <v>1.7354</v>
       </c>
       <c r="H158" t="n">
-        <v>49.37</v>
+        <v>49.3689</v>
       </c>
       <c r="I158" t="n">
-        <v>48.72</v>
+        <v>48.7221</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.65</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>222081</v>
       </c>
       <c r="O158" t="n">
-        <v>80.83</v>
+        <v>80.8284</v>
       </c>
       <c r="P158" t="inlineStr">
         <is>
@@ -11832,16 +11832,16 @@
         <v>10659</v>
       </c>
       <c r="G159" t="n">
-        <v>4.05</v>
+        <v>4.049</v>
       </c>
       <c r="H159" t="n">
-        <v>49.57</v>
+        <v>49.5736</v>
       </c>
       <c r="I159" t="n">
-        <v>48.55</v>
+        <v>48.5463</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.03</v>
+        <v>-1.0273</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>193756</v>
       </c>
       <c r="O159" t="n">
-        <v>73.59</v>
+        <v>73.5873</v>
       </c>
       <c r="P159" t="inlineStr">
         <is>
@@ -11902,16 +11902,16 @@
         <v>3452</v>
       </c>
       <c r="G160" t="n">
-        <v>1.28</v>
+        <v>1.2785</v>
       </c>
       <c r="H160" t="n">
-        <v>49.22</v>
+        <v>49.2235</v>
       </c>
       <c r="I160" t="n">
-        <v>48.6</v>
+        <v>48.605</v>
       </c>
       <c r="J160" t="n">
-        <v>-0.62</v>
+        <v>-0.6186</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>200715</v>
       </c>
       <c r="O160" t="n">
-        <v>74.33</v>
+        <v>74.3326</v>
       </c>
       <c r="P160" t="inlineStr">
         <is>
@@ -11972,16 +11972,16 @@
         <v>3013</v>
       </c>
       <c r="G161" t="n">
-        <v>1.09</v>
+        <v>1.0915</v>
       </c>
       <c r="H161" t="n">
-        <v>49.18</v>
+        <v>49.1805</v>
       </c>
       <c r="I161" t="n">
-        <v>48.59</v>
+        <v>48.5853</v>
       </c>
       <c r="J161" t="n">
-        <v>-0.6</v>
+        <v>-0.5953000000000001</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>206117</v>
       </c>
       <c r="O161" t="n">
-        <v>74.67</v>
+        <v>74.6671</v>
       </c>
       <c r="P161" t="inlineStr">
         <is>
@@ -12042,16 +12042,16 @@
         <v>1821</v>
       </c>
       <c r="G162" t="n">
-        <v>0.73</v>
+        <v>0.728</v>
       </c>
       <c r="H162" t="n">
-        <v>48.75</v>
+        <v>48.7451</v>
       </c>
       <c r="I162" t="n">
-        <v>47.76</v>
+        <v>47.7555</v>
       </c>
       <c r="J162" t="n">
-        <v>-0.99</v>
+        <v>-0.9896</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>206140</v>
       </c>
       <c r="O162" t="n">
-        <v>82.40000000000001</v>
+        <v>82.4033</v>
       </c>
       <c r="P162" t="inlineStr">
         <is>
@@ -12112,16 +12112,16 @@
         <v>2733</v>
       </c>
       <c r="G163" t="n">
-        <v>0.97</v>
+        <v>0.9712</v>
       </c>
       <c r="H163" t="n">
-        <v>49.8</v>
+        <v>49.7955</v>
       </c>
       <c r="I163" t="n">
-        <v>48.92</v>
+        <v>48.9188</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.88</v>
+        <v>-0.8767</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>241576</v>
       </c>
       <c r="O163" t="n">
-        <v>85.84</v>
+        <v>85.84180000000001</v>
       </c>
       <c r="P163" t="inlineStr">
         <is>
@@ -12182,16 +12182,16 @@
         <v>10428</v>
       </c>
       <c r="G164" t="n">
-        <v>3.6</v>
+        <v>3.6042</v>
       </c>
       <c r="H164" t="n">
-        <v>49.51</v>
+        <v>49.5064</v>
       </c>
       <c r="I164" t="n">
-        <v>48.85</v>
+        <v>48.8537</v>
       </c>
       <c r="J164" t="n">
-        <v>-0.65</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>226929</v>
       </c>
       <c r="O164" t="n">
-        <v>78.43000000000001</v>
+        <v>78.42529999999999</v>
       </c>
       <c r="P164" t="inlineStr">
         <is>
@@ -12252,16 +12252,16 @@
         <v>13448</v>
       </c>
       <c r="G165" t="n">
-        <v>4.79</v>
+        <v>4.7861</v>
       </c>
       <c r="H165" t="n">
-        <v>49.88</v>
+        <v>49.8842</v>
       </c>
       <c r="I165" t="n">
-        <v>49.42</v>
+        <v>49.4216</v>
       </c>
       <c r="J165" t="n">
-        <v>-0.46</v>
+        <v>-0.4626</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>229452</v>
       </c>
       <c r="O165" t="n">
-        <v>81.65000000000001</v>
+        <v>81.65170000000001</v>
       </c>
       <c r="P165" t="inlineStr">
         <is>
@@ -12322,16 +12322,16 @@
         <v>-542</v>
       </c>
       <c r="G166" t="n">
-        <v>-0.2</v>
+        <v>-0.2047</v>
       </c>
       <c r="H166" t="n">
-        <v>49.21</v>
+        <v>49.213</v>
       </c>
       <c r="I166" t="n">
-        <v>48.57</v>
+        <v>48.5685</v>
       </c>
       <c r="J166" t="n">
-        <v>-0.64</v>
+        <v>-0.6445</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>222880</v>
       </c>
       <c r="O166" t="n">
-        <v>84.19</v>
+        <v>84.18729999999999</v>
       </c>
       <c r="P166" t="inlineStr">
         <is>
@@ -12392,16 +12392,16 @@
         <v>-3560</v>
       </c>
       <c r="G167" t="n">
-        <v>-1.34</v>
+        <v>-1.344</v>
       </c>
       <c r="H167" t="n">
-        <v>49.7</v>
+        <v>49.6999</v>
       </c>
       <c r="I167" t="n">
-        <v>49.12</v>
+        <v>49.1212</v>
       </c>
       <c r="J167" t="n">
-        <v>-0.58</v>
+        <v>-0.5787</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>234979</v>
       </c>
       <c r="O167" t="n">
-        <v>88.70999999999999</v>
+        <v>88.7132</v>
       </c>
       <c r="P167" t="inlineStr">
         <is>
@@ -12462,16 +12462,16 @@
         <v>11689</v>
       </c>
       <c r="G168" t="n">
-        <v>4.33</v>
+        <v>4.3348</v>
       </c>
       <c r="H168" t="n">
-        <v>49.99</v>
+        <v>49.9865</v>
       </c>
       <c r="I168" t="n">
-        <v>49.34</v>
+        <v>49.3383</v>
       </c>
       <c r="J168" t="n">
-        <v>-0.65</v>
+        <v>-0.6482</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>201758</v>
       </c>
       <c r="O168" t="n">
-        <v>74.8</v>
+        <v>74.8008</v>
       </c>
       <c r="P168" t="inlineStr">
         <is>
@@ -12532,16 +12532,16 @@
         <v>3580</v>
       </c>
       <c r="G169" t="n">
-        <v>1.28</v>
+        <v>1.2809</v>
       </c>
       <c r="H169" t="n">
-        <v>49.03</v>
+        <v>49.0298</v>
       </c>
       <c r="I169" t="n">
-        <v>48.84</v>
+        <v>48.8356</v>
       </c>
       <c r="J169" t="n">
-        <v>-0.19</v>
+        <v>-0.1942</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>235691</v>
       </c>
       <c r="O169" t="n">
-        <v>84.3</v>
+        <v>84.3018</v>
       </c>
       <c r="P169" t="inlineStr">
         <is>
@@ -12602,16 +12602,16 @@
         <v>20815</v>
       </c>
       <c r="G170" t="n">
-        <v>7.71</v>
+        <v>7.7063</v>
       </c>
       <c r="H170" t="n">
-        <v>49.78</v>
+        <v>49.7766</v>
       </c>
       <c r="I170" t="n">
-        <v>49.57</v>
+        <v>49.5696</v>
       </c>
       <c r="J170" t="n">
-        <v>-0.21</v>
+        <v>-0.207</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>217079</v>
       </c>
       <c r="O170" t="n">
-        <v>80.33</v>
+        <v>80.32640000000001</v>
       </c>
       <c r="P170" t="inlineStr">
         <is>
@@ -12672,16 +12672,16 @@
         <v>11858</v>
       </c>
       <c r="G171" t="n">
-        <v>4.29</v>
+        <v>4.2947</v>
       </c>
       <c r="H171" t="n">
-        <v>50.03</v>
+        <v>50.0282</v>
       </c>
       <c r="I171" t="n">
-        <v>49.49</v>
+        <v>49.4899</v>
       </c>
       <c r="J171" t="n">
-        <v>-0.54</v>
+        <v>-0.5384</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>237550</v>
       </c>
       <c r="O171" t="n">
-        <v>86.02</v>
+        <v>86.0196</v>
       </c>
       <c r="P171" t="inlineStr">
         <is>
@@ -12742,16 +12742,16 @@
         <v>799</v>
       </c>
       <c r="G172" t="n">
-        <v>0.29</v>
+        <v>0.2906</v>
       </c>
       <c r="H172" t="n">
-        <v>49.47</v>
+        <v>49.4746</v>
       </c>
       <c r="I172" t="n">
-        <v>49.16</v>
+        <v>49.1596</v>
       </c>
       <c r="J172" t="n">
-        <v>-0.32</v>
+        <v>-0.315</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>218644</v>
       </c>
       <c r="O172" t="n">
-        <v>79.51000000000001</v>
+        <v>79.5107</v>
       </c>
       <c r="P172" t="inlineStr">
         <is>
@@ -12812,16 +12812,16 @@
         <v>3651</v>
       </c>
       <c r="G173" t="n">
-        <v>1.41</v>
+        <v>1.4094</v>
       </c>
       <c r="H173" t="n">
-        <v>49.95</v>
+        <v>49.9544</v>
       </c>
       <c r="I173" t="n">
-        <v>49.46</v>
+        <v>49.4563</v>
       </c>
       <c r="J173" t="n">
-        <v>-0.5</v>
+        <v>-0.4981</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>218922</v>
       </c>
       <c r="O173" t="n">
-        <v>84.5</v>
+        <v>84.5017</v>
       </c>
       <c r="P173" t="inlineStr">
         <is>
@@ -12882,13 +12882,13 @@
         <v>5425</v>
       </c>
       <c r="G174" t="n">
-        <v>2.35</v>
+        <v>2.3514</v>
       </c>
       <c r="H174" t="n">
-        <v>48.99</v>
+        <v>48.9851</v>
       </c>
       <c r="I174" t="n">
-        <v>48.41</v>
+        <v>48.4051</v>
       </c>
       <c r="J174" t="n">
         <v>-0.58</v>
@@ -12910,7 +12910,7 @@
         <v>163428</v>
       </c>
       <c r="O174" t="n">
-        <v>70.69</v>
+        <v>70.6914</v>
       </c>
       <c r="P174" t="inlineStr">
         <is>
@@ -12952,16 +12952,16 @@
         <v>5553</v>
       </c>
       <c r="G175" t="n">
-        <v>2.45</v>
+        <v>2.4525</v>
       </c>
       <c r="H175" t="n">
-        <v>48.61</v>
+        <v>48.6075</v>
       </c>
       <c r="I175" t="n">
-        <v>48.17</v>
+        <v>48.1697</v>
       </c>
       <c r="J175" t="n">
-        <v>-0.44</v>
+        <v>-0.4377</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>155916</v>
       </c>
       <c r="O175" t="n">
-        <v>68.84999999999999</v>
+        <v>68.84829999999999</v>
       </c>
       <c r="P175" t="inlineStr">
         <is>
@@ -13022,16 +13022,16 @@
         <v>7464</v>
       </c>
       <c r="G176" t="n">
-        <v>3.22</v>
+        <v>3.2156</v>
       </c>
       <c r="H176" t="n">
-        <v>49.29</v>
+        <v>49.2913</v>
       </c>
       <c r="I176" t="n">
-        <v>49.02</v>
+        <v>49.0154</v>
       </c>
       <c r="J176" t="n">
-        <v>-0.28</v>
+        <v>-0.2759</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>175794</v>
       </c>
       <c r="O176" t="n">
-        <v>75.70999999999999</v>
+        <v>75.7132</v>
       </c>
       <c r="P176" t="inlineStr">
         <is>
@@ -13092,16 +13092,16 @@
         <v>2518</v>
       </c>
       <c r="G177" t="n">
-        <v>1.06</v>
+        <v>1.0556</v>
       </c>
       <c r="H177" t="n">
-        <v>48.67</v>
+        <v>48.6691</v>
       </c>
       <c r="I177" t="n">
-        <v>48.28</v>
+        <v>48.2833</v>
       </c>
       <c r="J177" t="n">
-        <v>-0.39</v>
+        <v>-0.3858</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>189003</v>
       </c>
       <c r="O177" t="n">
-        <v>79.22</v>
+        <v>79.2183</v>
       </c>
       <c r="P177" t="inlineStr">
         <is>
@@ -13162,16 +13162,16 @@
         <v>10877</v>
       </c>
       <c r="G178" t="n">
-        <v>3.67</v>
+        <v>3.6653</v>
       </c>
       <c r="H178" t="n">
-        <v>49.76</v>
+        <v>49.7555</v>
       </c>
       <c r="I178" t="n">
-        <v>49.2</v>
+        <v>49.2011</v>
       </c>
       <c r="J178" t="n">
-        <v>-0.55</v>
+        <v>-0.5545</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>222014</v>
       </c>
       <c r="O178" t="n">
-        <v>74.77</v>
+        <v>74.77379999999999</v>
       </c>
       <c r="P178" t="inlineStr">
         <is>
@@ -13232,16 +13232,16 @@
         <v>1927</v>
       </c>
       <c r="G179" t="n">
-        <v>0.71</v>
+        <v>0.7109</v>
       </c>
       <c r="H179" t="n">
-        <v>49.7</v>
+        <v>49.6999</v>
       </c>
       <c r="I179" t="n">
-        <v>49.42</v>
+        <v>49.4204</v>
       </c>
       <c r="J179" t="n">
-        <v>-0.28</v>
+        <v>-0.2795</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>222222</v>
       </c>
       <c r="O179" t="n">
-        <v>81.95999999999999</v>
+        <v>81.9602</v>
       </c>
       <c r="P179" t="inlineStr">
         <is>
@@ -13302,13 +13302,13 @@
         <v>5512</v>
       </c>
       <c r="G180" t="n">
-        <v>2.17</v>
+        <v>2.1683</v>
       </c>
       <c r="H180" t="n">
-        <v>49.77</v>
+        <v>49.7748</v>
       </c>
       <c r="I180" t="n">
-        <v>49.42</v>
+        <v>49.4248</v>
       </c>
       <c r="J180" t="n">
         <v>-0.35</v>
@@ -13330,7 +13330,7 @@
         <v>189771</v>
       </c>
       <c r="O180" t="n">
-        <v>74.63</v>
+        <v>74.63420000000001</v>
       </c>
       <c r="P180" t="inlineStr">
         <is>
@@ -13372,16 +13372,16 @@
         <v>43319</v>
       </c>
       <c r="G181" t="n">
-        <v>15.48</v>
+        <v>15.4825</v>
       </c>
       <c r="H181" t="n">
-        <v>48.85</v>
+        <v>48.8513</v>
       </c>
       <c r="I181" t="n">
-        <v>48.77</v>
+        <v>48.7701</v>
       </c>
       <c r="J181" t="n">
-        <v>-0.08</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -13442,16 +13442,16 @@
         <v>3814</v>
       </c>
       <c r="G182" t="n">
-        <v>1.51</v>
+        <v>1.509</v>
       </c>
       <c r="H182" t="n">
-        <v>49.33</v>
+        <v>49.3319</v>
       </c>
       <c r="I182" t="n">
-        <v>48.88</v>
+        <v>48.8834</v>
       </c>
       <c r="J182" t="n">
-        <v>-0.45</v>
+        <v>-0.4485</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         <v>184481</v>
       </c>
       <c r="O182" t="n">
-        <v>72.95999999999999</v>
+        <v>72.95569999999999</v>
       </c>
       <c r="P182" t="inlineStr">
         <is>
@@ -13512,16 +13512,16 @@
         <v>3550</v>
       </c>
       <c r="G183" t="n">
-        <v>1.44</v>
+        <v>1.4357</v>
       </c>
       <c r="H183" t="n">
-        <v>48.98</v>
+        <v>48.9825</v>
       </c>
       <c r="I183" t="n">
-        <v>48.55</v>
+        <v>48.5463</v>
       </c>
       <c r="J183" t="n">
-        <v>-0.44</v>
+        <v>-0.4362</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>200485</v>
       </c>
       <c r="O183" t="n">
-        <v>80.88</v>
+        <v>80.8763</v>
       </c>
       <c r="P183" t="inlineStr">
         <is>
@@ -13582,16 +13582,16 @@
         <v>133</v>
       </c>
       <c r="G184" t="n">
-        <v>0.05</v>
+        <v>0.0535</v>
       </c>
       <c r="H184" t="n">
-        <v>49.21</v>
+        <v>49.2128</v>
       </c>
       <c r="I184" t="n">
-        <v>49.09</v>
+        <v>49.0935</v>
       </c>
       <c r="J184" t="n">
-        <v>-0.12</v>
+        <v>-0.1193</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>199529</v>
       </c>
       <c r="O184" t="n">
-        <v>80.22</v>
+        <v>80.2178</v>
       </c>
       <c r="P184" t="inlineStr">
         <is>
@@ -13652,16 +13652,16 @@
         <v>-909</v>
       </c>
       <c r="G185" t="n">
-        <v>-0.33</v>
+        <v>-0.3327</v>
       </c>
       <c r="H185" t="n">
-        <v>47.83</v>
+        <v>47.8346</v>
       </c>
       <c r="I185" t="n">
-        <v>47.76</v>
+        <v>47.765</v>
       </c>
       <c r="J185" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0696</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -13680,7 +13680,7 @@
         <v>224991</v>
       </c>
       <c r="O185" t="n">
-        <v>82.23999999999999</v>
+        <v>82.2393</v>
       </c>
       <c r="P185" t="inlineStr">
         <is>
@@ -13722,16 +13722,16 @@
         <v>3362</v>
       </c>
       <c r="G186" t="n">
-        <v>1.21</v>
+        <v>1.2105</v>
       </c>
       <c r="H186" t="n">
-        <v>48.15</v>
+        <v>48.1468</v>
       </c>
       <c r="I186" t="n">
         <v>47.76</v>
       </c>
       <c r="J186" t="n">
-        <v>-0.39</v>
+        <v>-0.3868</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>206025</v>
       </c>
       <c r="O186" t="n">
-        <v>74.15000000000001</v>
+        <v>74.1468</v>
       </c>
       <c r="P186" t="inlineStr">
         <is>
@@ -13792,13 +13792,13 @@
         <v>2951</v>
       </c>
       <c r="G187" t="n">
-        <v>0.95</v>
+        <v>0.9543</v>
       </c>
       <c r="H187" t="n">
-        <v>48.97</v>
+        <v>48.9687</v>
       </c>
       <c r="I187" t="n">
-        <v>48.75</v>
+        <v>48.7486</v>
       </c>
       <c r="J187" t="n">
         <v>-0.22</v>
@@ -13820,7 +13820,7 @@
         <v>239054</v>
       </c>
       <c r="O187" t="n">
-        <v>77.28</v>
+        <v>77.2782</v>
       </c>
       <c r="P187" t="inlineStr">
         <is>
@@ -13862,16 +13862,16 @@
         <v>4006</v>
       </c>
       <c r="G188" t="n">
-        <v>1.91</v>
+        <v>1.9081</v>
       </c>
       <c r="H188" t="n">
-        <v>48.04</v>
+        <v>48.0407</v>
       </c>
       <c r="I188" t="n">
-        <v>47.68</v>
+        <v>47.6817</v>
       </c>
       <c r="J188" t="n">
-        <v>-0.36</v>
+        <v>-0.3591</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>163162</v>
       </c>
       <c r="O188" t="n">
-        <v>77.69</v>
+        <v>77.68989999999999</v>
       </c>
       <c r="P188" t="inlineStr">
         <is>
@@ -13932,16 +13932,16 @@
         <v>9481</v>
       </c>
       <c r="G189" t="n">
-        <v>4.52</v>
+        <v>4.5176</v>
       </c>
       <c r="H189" t="n">
-        <v>48.15</v>
+        <v>48.1491</v>
       </c>
       <c r="I189" t="n">
-        <v>47.7</v>
+        <v>47.6965</v>
       </c>
       <c r="J189" t="n">
-        <v>-0.45</v>
+        <v>-0.4526</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>167505</v>
       </c>
       <c r="O189" t="n">
-        <v>79.79000000000001</v>
+        <v>79.79430000000001</v>
       </c>
       <c r="P189" t="inlineStr">
         <is>
@@ -14002,16 +14002,16 @@
         <v>25218</v>
       </c>
       <c r="G190" t="n">
-        <v>9.869999999999999</v>
+        <v>9.866</v>
       </c>
       <c r="H190" t="n">
-        <v>49.08</v>
+        <v>49.0804</v>
       </c>
       <c r="I190" t="n">
-        <v>49</v>
+        <v>49.0032</v>
       </c>
       <c r="J190" t="n">
-        <v>-0.08</v>
+        <v>-0.0772</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>191704</v>
       </c>
       <c r="O190" t="n">
-        <v>74.95999999999999</v>
+        <v>74.9623</v>
       </c>
       <c r="P190" t="inlineStr">
         <is>
@@ -14072,16 +14072,16 @@
         <v>-4247</v>
       </c>
       <c r="G191" t="n">
-        <v>-1.73</v>
+        <v>-1.7345</v>
       </c>
       <c r="H191" t="n">
-        <v>48.89</v>
+        <v>48.8883</v>
       </c>
       <c r="I191" t="n">
-        <v>49.48</v>
+        <v>49.4799</v>
       </c>
       <c r="J191" t="n">
-        <v>0.59</v>
+        <v>0.5916</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>183199</v>
       </c>
       <c r="O191" t="n">
-        <v>74.79000000000001</v>
+        <v>74.7876</v>
       </c>
       <c r="P191" t="inlineStr">
         <is>
@@ -14142,16 +14142,16 @@
         <v>14459</v>
       </c>
       <c r="G192" t="n">
-        <v>4.98</v>
+        <v>4.9835</v>
       </c>
       <c r="H192" t="n">
-        <v>48.46</v>
+        <v>48.4595</v>
       </c>
       <c r="I192" t="n">
-        <v>48.34</v>
+        <v>48.3397</v>
       </c>
       <c r="J192" t="n">
-        <v>-0.12</v>
+        <v>-0.1198</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>223405</v>
       </c>
       <c r="O192" t="n">
-        <v>76.95999999999999</v>
+        <v>76.95529999999999</v>
       </c>
       <c r="P192" t="inlineStr">
         <is>
@@ -14212,16 +14212,16 @@
         <v>2824</v>
       </c>
       <c r="G193" t="n">
-        <v>1.14</v>
+        <v>1.1387</v>
       </c>
       <c r="H193" t="n">
-        <v>47.95</v>
+        <v>47.9518</v>
       </c>
       <c r="I193" t="n">
-        <v>47.9</v>
+        <v>47.896</v>
       </c>
       <c r="J193" t="n">
-        <v>-0.06</v>
+        <v>-0.0558</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>195331</v>
       </c>
       <c r="O193" t="n">
-        <v>78.73999999999999</v>
+        <v>78.7431</v>
       </c>
       <c r="P193" t="inlineStr">
         <is>
@@ -14282,16 +14282,16 @@
         <v>4655</v>
       </c>
       <c r="G194" t="n">
-        <v>2.15</v>
+        <v>2.1453</v>
       </c>
       <c r="H194" t="n">
-        <v>48.35</v>
+        <v>48.3495</v>
       </c>
       <c r="I194" t="n">
-        <v>48.07</v>
+        <v>48.0724</v>
       </c>
       <c r="J194" t="n">
-        <v>-0.28</v>
+        <v>-0.2771</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>176064</v>
       </c>
       <c r="O194" t="n">
-        <v>81.13</v>
+        <v>81.125</v>
       </c>
       <c r="P194" t="inlineStr">
         <is>
@@ -14352,16 +14352,16 @@
         <v>-3524</v>
       </c>
       <c r="G195" t="n">
-        <v>-1.52</v>
+        <v>-1.5212</v>
       </c>
       <c r="H195" t="n">
-        <v>48.52</v>
+        <v>48.5224</v>
       </c>
       <c r="I195" t="n">
-        <v>48.31</v>
+        <v>48.3145</v>
       </c>
       <c r="J195" t="n">
-        <v>-0.21</v>
+        <v>-0.2079</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>190636</v>
       </c>
       <c r="O195" t="n">
-        <v>82.28</v>
+        <v>82.28449999999999</v>
       </c>
       <c r="P195" t="inlineStr">
         <is>
@@ -14422,16 +14422,16 @@
         <v>8516</v>
       </c>
       <c r="G196" t="n">
-        <v>3.53</v>
+        <v>3.5346</v>
       </c>
       <c r="H196" t="n">
-        <v>48.46</v>
+        <v>48.4556</v>
       </c>
       <c r="I196" t="n">
-        <v>47.97</v>
+        <v>47.9743</v>
       </c>
       <c r="J196" t="n">
-        <v>-0.48</v>
+        <v>-0.4813</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>188597</v>
       </c>
       <c r="O196" t="n">
-        <v>78.26000000000001</v>
+        <v>78.2628</v>
       </c>
       <c r="P196" t="inlineStr">
         <is>
@@ -14492,16 +14492,16 @@
         <v>-2091</v>
       </c>
       <c r="G197" t="n">
-        <v>-0.86</v>
+        <v>-0.8551</v>
       </c>
       <c r="H197" t="n">
-        <v>47.89</v>
+        <v>47.8868</v>
       </c>
       <c r="I197" t="n">
-        <v>47.57</v>
+        <v>47.5708</v>
       </c>
       <c r="J197" t="n">
-        <v>-0.32</v>
+        <v>-0.316</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>198583</v>
       </c>
       <c r="O197" t="n">
-        <v>81.2</v>
+        <v>81.1968</v>
       </c>
       <c r="P197" t="inlineStr">
         <is>
@@ -14562,16 +14562,16 @@
         <v>255</v>
       </c>
       <c r="G198" t="n">
-        <v>0.1</v>
+        <v>0.0963</v>
       </c>
       <c r="H198" t="n">
-        <v>49.31</v>
+        <v>49.3129</v>
       </c>
       <c r="I198" t="n">
-        <v>49.07</v>
+        <v>49.0651</v>
       </c>
       <c r="J198" t="n">
-        <v>-0.25</v>
+        <v>-0.2478</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>213166</v>
       </c>
       <c r="O198" t="n">
-        <v>80.53</v>
+        <v>80.53270000000001</v>
       </c>
       <c r="P198" t="inlineStr">
         <is>
@@ -14632,16 +14632,16 @@
         <v>8691</v>
       </c>
       <c r="G199" t="n">
-        <v>2.92</v>
+        <v>2.9183</v>
       </c>
       <c r="H199" t="n">
-        <v>49.1</v>
+        <v>49.0984</v>
       </c>
       <c r="I199" t="n">
-        <v>48.59</v>
+        <v>48.5855</v>
       </c>
       <c r="J199" t="n">
-        <v>-0.51</v>
+        <v>-0.5129</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>233271</v>
       </c>
       <c r="O199" t="n">
-        <v>78.3</v>
+        <v>78.3009</v>
       </c>
       <c r="P199" t="inlineStr">
         <is>
@@ -14702,16 +14702,16 @@
         <v>5477</v>
       </c>
       <c r="G200" t="n">
-        <v>2.22</v>
+        <v>2.217</v>
       </c>
       <c r="H200" t="n">
-        <v>48.47</v>
+        <v>48.4705</v>
       </c>
       <c r="I200" t="n">
-        <v>48.09</v>
+        <v>48.0896</v>
       </c>
       <c r="J200" t="n">
-        <v>-0.38</v>
+        <v>-0.381</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>203064</v>
       </c>
       <c r="O200" t="n">
-        <v>82.16</v>
+        <v>82.16030000000001</v>
       </c>
       <c r="P200" t="inlineStr">
         <is>
@@ -14772,16 +14772,16 @@
         <v>2925</v>
       </c>
       <c r="G201" t="n">
-        <v>1.1</v>
+        <v>1.0977</v>
       </c>
       <c r="H201" t="n">
-        <v>48.58</v>
+        <v>48.5784</v>
       </c>
       <c r="I201" t="n">
-        <v>47.89</v>
+        <v>47.8923</v>
       </c>
       <c r="J201" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.6861</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>225524</v>
       </c>
       <c r="O201" t="n">
-        <v>84.62</v>
+        <v>84.6215</v>
       </c>
       <c r="P201" t="inlineStr">
         <is>
@@ -14909,16 +14909,16 @@
         <v>16774</v>
       </c>
       <c r="F2" t="n">
-        <v>5.68</v>
+        <v>5.6832</v>
       </c>
       <c r="G2" t="n">
-        <v>49.09</v>
+        <v>49.0884</v>
       </c>
       <c r="H2" t="n">
-        <v>48.26</v>
+        <v>48.2604</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.83</v>
+        <v>-0.828</v>
       </c>
     </row>
     <row r="3">
@@ -14940,16 +14940,16 @@
         <v>114100</v>
       </c>
       <c r="F3" t="n">
-        <v>5.16</v>
+        <v>5.1581</v>
       </c>
       <c r="G3" t="n">
-        <v>48</v>
+        <v>48.0041</v>
       </c>
       <c r="H3" t="n">
-        <v>47.91</v>
+        <v>47.9096</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09</v>
+        <v>-0.0945</v>
       </c>
     </row>
     <row r="4">
@@ -14971,16 +14971,16 @@
         <v>85964</v>
       </c>
       <c r="F4" t="n">
-        <v>4.55</v>
+        <v>4.5481</v>
       </c>
       <c r="G4" t="n">
-        <v>49.17</v>
+        <v>49.1648</v>
       </c>
       <c r="H4" t="n">
-        <v>48.45</v>
+        <v>48.4543</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.72</v>
+        <v>-0.7105</v>
       </c>
     </row>
     <row r="5">
@@ -15002,16 +15002,16 @@
         <v>64609</v>
       </c>
       <c r="F5" t="n">
-        <v>4.46</v>
+        <v>4.4646</v>
       </c>
       <c r="G5" t="n">
-        <v>49.18</v>
+        <v>49.1843</v>
       </c>
       <c r="H5" t="n">
-        <v>48.78</v>
+        <v>48.7787</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4</v>
+        <v>-0.4056</v>
       </c>
     </row>
     <row r="6">
@@ -15033,16 +15033,16 @@
         <v>202398</v>
       </c>
       <c r="F6" t="n">
-        <v>4.36</v>
+        <v>4.3644</v>
       </c>
       <c r="G6" t="n">
-        <v>47.9</v>
+        <v>47.8995</v>
       </c>
       <c r="H6" t="n">
-        <v>48.04</v>
+        <v>48.0391</v>
       </c>
       <c r="I6" t="n">
-        <v>0.14</v>
+        <v>0.1396</v>
       </c>
     </row>
     <row r="7">
@@ -15064,16 +15064,16 @@
         <v>69132</v>
       </c>
       <c r="F7" t="n">
-        <v>3.74</v>
+        <v>3.7358</v>
       </c>
       <c r="G7" t="n">
-        <v>49.38</v>
+        <v>49.3792</v>
       </c>
       <c r="H7" t="n">
-        <v>49.06</v>
+        <v>49.0593</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.32</v>
+        <v>-0.3199</v>
       </c>
     </row>
     <row r="8">
@@ -15095,16 +15095,16 @@
         <v>48741</v>
       </c>
       <c r="F8" t="n">
-        <v>3.56</v>
+        <v>3.5569</v>
       </c>
       <c r="G8" t="n">
-        <v>49.66</v>
+        <v>49.6557</v>
       </c>
       <c r="H8" t="n">
-        <v>49.27</v>
+        <v>49.2702</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.39</v>
+        <v>-0.3855</v>
       </c>
     </row>
     <row r="9">
@@ -15126,16 +15126,16 @@
         <v>51741</v>
       </c>
       <c r="F9" t="n">
-        <v>3.55</v>
+        <v>3.5478</v>
       </c>
       <c r="G9" t="n">
-        <v>48.45</v>
+        <v>48.449</v>
       </c>
       <c r="H9" t="n">
-        <v>48.39</v>
+        <v>48.385</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06</v>
+        <v>-0.064</v>
       </c>
     </row>
     <row r="10">
@@ -15157,16 +15157,16 @@
         <v>27180</v>
       </c>
       <c r="F10" t="n">
-        <v>3.33</v>
+        <v>3.3298</v>
       </c>
       <c r="G10" t="n">
-        <v>47.84</v>
+        <v>47.8444</v>
       </c>
       <c r="H10" t="n">
-        <v>47.62</v>
+        <v>47.6207</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.22</v>
+        <v>-0.2237</v>
       </c>
     </row>
     <row r="11">
@@ -15188,16 +15188,16 @@
         <v>44020</v>
       </c>
       <c r="F11" t="n">
-        <v>3.02</v>
+        <v>3.0168</v>
       </c>
       <c r="G11" t="n">
-        <v>48.12</v>
+        <v>48.1193</v>
       </c>
       <c r="H11" t="n">
-        <v>47.74</v>
+        <v>47.7374</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.38</v>
+        <v>-0.3819</v>
       </c>
     </row>
     <row r="12">
@@ -15219,16 +15219,16 @@
         <v>19199</v>
       </c>
       <c r="F12" t="n">
-        <v>2.55</v>
+        <v>2.5465</v>
       </c>
       <c r="G12" t="n">
-        <v>47.38</v>
+        <v>47.383</v>
       </c>
       <c r="H12" t="n">
-        <v>46.99</v>
+        <v>46.9898</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.39</v>
+        <v>-0.3932</v>
       </c>
     </row>
     <row r="13">
@@ -15250,16 +15250,16 @@
         <v>20960</v>
       </c>
       <c r="F13" t="n">
-        <v>2.26</v>
+        <v>2.2592</v>
       </c>
       <c r="G13" t="n">
-        <v>48.89</v>
+        <v>48.8883</v>
       </c>
       <c r="H13" t="n">
-        <v>48.47</v>
+        <v>48.4673</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.42</v>
+        <v>-0.421</v>
       </c>
     </row>
     <row r="14">
@@ -15281,16 +15281,16 @@
         <v>24506</v>
       </c>
       <c r="F14" t="n">
-        <v>2.22</v>
+        <v>2.2173</v>
       </c>
       <c r="G14" t="n">
-        <v>48.59</v>
+        <v>48.5866</v>
       </c>
       <c r="H14" t="n">
-        <v>48.02</v>
+        <v>48.019</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.57</v>
+        <v>-0.5676</v>
       </c>
     </row>
     <row r="15">
@@ -15312,16 +15312,16 @@
         <v>21128</v>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>2.0802</v>
       </c>
       <c r="G15" t="n">
-        <v>46.6</v>
+        <v>46.605</v>
       </c>
       <c r="H15" t="n">
-        <v>46.39</v>
+        <v>46.3856</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.21</v>
+        <v>-0.2194</v>
       </c>
     </row>
     <row r="16">
@@ -15343,16 +15343,16 @@
         <v>35632</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1.995</v>
       </c>
       <c r="G16" t="n">
-        <v>47.3</v>
+        <v>47.3058</v>
       </c>
       <c r="H16" t="n">
-        <v>47.17</v>
+        <v>47.1699</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.13</v>
+        <v>-0.1359</v>
       </c>
     </row>
     <row r="17">
@@ -15374,16 +15374,16 @@
         <v>18945</v>
       </c>
       <c r="F17" t="n">
-        <v>1.79</v>
+        <v>1.7882</v>
       </c>
       <c r="G17" t="n">
-        <v>49.19</v>
+        <v>49.1863</v>
       </c>
       <c r="H17" t="n">
-        <v>48.38</v>
+        <v>48.3828</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.8035</v>
       </c>
     </row>
     <row r="18">
@@ -15405,16 +15405,16 @@
         <v>31647</v>
       </c>
       <c r="F18" t="n">
-        <v>1.76</v>
+        <v>1.7561</v>
       </c>
       <c r="G18" t="n">
-        <v>47.71</v>
+        <v>47.7147</v>
       </c>
       <c r="H18" t="n">
-        <v>47.19</v>
+        <v>47.1895</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.52</v>
+        <v>-0.5252</v>
       </c>
     </row>
     <row r="19">
@@ -15436,16 +15436,16 @@
         <v>22507</v>
       </c>
       <c r="F19" t="n">
-        <v>1.63</v>
+        <v>1.6294</v>
       </c>
       <c r="G19" t="n">
-        <v>49.62</v>
+        <v>49.623</v>
       </c>
       <c r="H19" t="n">
-        <v>48.98</v>
+        <v>48.976</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.64</v>
+        <v>-0.647</v>
       </c>
     </row>
     <row r="20">
@@ -15467,16 +15467,16 @@
         <v>17348</v>
       </c>
       <c r="F20" t="n">
-        <v>1.61</v>
+        <v>1.6123</v>
       </c>
       <c r="G20" t="n">
-        <v>48.88</v>
+        <v>48.8782</v>
       </c>
       <c r="H20" t="n">
-        <v>48.42</v>
+        <v>48.4196</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.46</v>
+        <v>-0.4586</v>
       </c>
     </row>
     <row r="21">
@@ -15498,16 +15498,16 @@
         <v>21002</v>
       </c>
       <c r="F21" t="n">
-        <v>1.59</v>
+        <v>1.5915</v>
       </c>
       <c r="G21" t="n">
-        <v>48.35</v>
+        <v>48.356</v>
       </c>
       <c r="H21" t="n">
-        <v>47.99</v>
+        <v>47.9941</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.36</v>
+        <v>-0.3619</v>
       </c>
     </row>
     <row r="22">
@@ -15529,16 +15529,16 @@
         <v>8419</v>
       </c>
       <c r="F22" t="n">
-        <v>1.58</v>
+        <v>1.5772</v>
       </c>
       <c r="G22" t="n">
-        <v>49.65</v>
+        <v>49.653</v>
       </c>
       <c r="H22" t="n">
-        <v>49.08</v>
+        <v>49.079</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.57</v>
+        <v>-0.574</v>
       </c>
     </row>
     <row r="23">
@@ -15560,16 +15560,16 @@
         <v>21499</v>
       </c>
       <c r="F23" t="n">
-        <v>1.57</v>
+        <v>1.5749</v>
       </c>
       <c r="G23" t="n">
-        <v>48.21</v>
+        <v>48.2129</v>
       </c>
       <c r="H23" t="n">
-        <v>47.85</v>
+        <v>47.8468</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.36</v>
+        <v>-0.3661</v>
       </c>
     </row>
     <row r="24">
@@ -15591,16 +15591,16 @@
         <v>34381</v>
       </c>
       <c r="F24" t="n">
-        <v>1.56</v>
+        <v>1.5643</v>
       </c>
       <c r="G24" t="n">
-        <v>47.71</v>
+        <v>47.7085</v>
       </c>
       <c r="H24" t="n">
-        <v>47.35</v>
+        <v>47.3561</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.36</v>
+        <v>-0.3524</v>
       </c>
     </row>
     <row r="25">
@@ -15622,16 +15622,16 @@
         <v>15588</v>
       </c>
       <c r="F25" t="n">
-        <v>1.41</v>
+        <v>1.4107</v>
       </c>
       <c r="G25" t="n">
-        <v>46.72</v>
+        <v>46.7217</v>
       </c>
       <c r="H25" t="n">
-        <v>46.18</v>
+        <v>46.1827</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.54</v>
+        <v>-0.539</v>
       </c>
     </row>
     <row r="26">
@@ -15653,16 +15653,16 @@
         <v>11056</v>
       </c>
       <c r="F26" t="n">
-        <v>1.32</v>
+        <v>1.3195</v>
       </c>
       <c r="G26" t="n">
-        <v>48.78</v>
+        <v>48.7828</v>
       </c>
       <c r="H26" t="n">
-        <v>48.47</v>
+        <v>48.4657</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.31</v>
+        <v>-0.3171</v>
       </c>
     </row>
     <row r="27">
@@ -15684,16 +15684,16 @@
         <v>13298</v>
       </c>
       <c r="F27" t="n">
-        <v>1.11</v>
+        <v>1.1058</v>
       </c>
       <c r="G27" t="n">
-        <v>46.94</v>
+        <v>46.9433</v>
       </c>
       <c r="H27" t="n">
-        <v>46.63</v>
+        <v>46.6231</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.31</v>
+        <v>-0.3202</v>
       </c>
     </row>
     <row r="28">
@@ -15715,16 +15715,16 @@
         <v>11954</v>
       </c>
       <c r="F28" t="n">
-        <v>0.82</v>
+        <v>0.8214</v>
       </c>
       <c r="G28" t="n">
-        <v>47.18</v>
+        <v>47.182</v>
       </c>
       <c r="H28" t="n">
-        <v>46.92</v>
+        <v>46.9192</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.26</v>
+        <v>-0.2628</v>
       </c>
     </row>
     <row r="29">
@@ -15746,16 +15746,16 @@
         <v>7556</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8089</v>
       </c>
       <c r="G29" t="n">
-        <v>48.3</v>
+        <v>48.2986</v>
       </c>
       <c r="H29" t="n">
-        <v>47.97</v>
+        <v>47.9757</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.33</v>
+        <v>-0.3229</v>
       </c>
     </row>
     <row r="30">
@@ -15777,16 +15777,16 @@
         <v>11782</v>
       </c>
       <c r="F30" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="G30" t="n">
-        <v>46.98</v>
+        <v>46.9842</v>
       </c>
       <c r="H30" t="n">
-        <v>46.86</v>
+        <v>46.8587</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.12</v>
+        <v>-0.1255</v>
       </c>
     </row>
     <row r="31">
@@ -15808,16 +15808,16 @@
         <v>10253</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6885</v>
       </c>
       <c r="G31" t="n">
-        <v>47.58</v>
+        <v>47.5783</v>
       </c>
       <c r="H31" t="n">
-        <v>47.68</v>
+        <v>47.6826</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1</v>
+        <v>0.1043</v>
       </c>
     </row>
     <row r="32">
@@ -15839,78 +15839,78 @@
         <v>10930</v>
       </c>
       <c r="F32" t="n">
-        <v>0.67</v>
+        <v>0.6674</v>
       </c>
       <c r="G32" t="n">
-        <v>47.84</v>
+        <v>47.8433</v>
       </c>
       <c r="H32" t="n">
-        <v>47.43</v>
+        <v>47.429</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.41</v>
+        <v>-0.4143</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Karauli</t>
+          <t>Bundi</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>1086542</v>
+        <v>860183</v>
       </c>
       <c r="D33" t="n">
-        <v>1079730</v>
+        <v>854779</v>
       </c>
       <c r="E33" t="n">
-        <v>6812</v>
+        <v>5404</v>
       </c>
       <c r="F33" t="n">
-        <v>0.63</v>
+        <v>0.6282</v>
       </c>
       <c r="G33" t="n">
-        <v>45.98</v>
+        <v>48.3431</v>
       </c>
       <c r="H33" t="n">
-        <v>45.87</v>
+        <v>48.1158</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.11</v>
+        <v>-0.2273</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Bundi</t>
+          <t>Karauli</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>860183</v>
+        <v>1086542</v>
       </c>
       <c r="D34" t="n">
-        <v>854779</v>
+        <v>1079730</v>
       </c>
       <c r="E34" t="n">
-        <v>5404</v>
+        <v>6812</v>
       </c>
       <c r="F34" t="n">
-        <v>0.63</v>
+        <v>0.6269</v>
       </c>
       <c r="G34" t="n">
-        <v>48.34</v>
+        <v>45.9797</v>
       </c>
       <c r="H34" t="n">
-        <v>48.11</v>
+        <v>45.8742</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.23</v>
+        <v>-0.1055</v>
       </c>
     </row>
     <row r="35">
@@ -15932,16 +15932,16 @@
         <v>5056</v>
       </c>
       <c r="F35" t="n">
-        <v>0.36</v>
+        <v>0.3622</v>
       </c>
       <c r="G35" t="n">
-        <v>47.75</v>
+        <v>47.7528</v>
       </c>
       <c r="H35" t="n">
-        <v>47.64</v>
+        <v>47.6341</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.11</v>
+        <v>-0.1187</v>
       </c>
     </row>
     <row r="36">
@@ -15963,16 +15963,16 @@
         <v>71</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01</v>
+        <v>0.0075</v>
       </c>
       <c r="G36" t="n">
-        <v>47.06</v>
+        <v>47.0566</v>
       </c>
       <c r="H36" t="n">
-        <v>46.98</v>
+        <v>46.9786</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.08</v>
+        <v>-0.078</v>
       </c>
     </row>
     <row r="37">
@@ -15994,16 +15994,16 @@
         <v>-1799</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.23</v>
+        <v>-0.2303</v>
       </c>
       <c r="G37" t="n">
-        <v>47.01</v>
+        <v>47.0155</v>
       </c>
       <c r="H37" t="n">
         <v>46.98</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.03</v>
+        <v>-0.0355</v>
       </c>
     </row>
     <row r="38">
@@ -16025,16 +16025,16 @@
         <v>-6012</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.78</v>
+        <v>-0.7813</v>
       </c>
       <c r="G38" t="n">
-        <v>46.73</v>
+        <v>46.7294</v>
       </c>
       <c r="H38" t="n">
-        <v>46.41</v>
+        <v>46.4078</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.32</v>
+        <v>-0.3216</v>
       </c>
     </row>
     <row r="39">
@@ -16056,16 +16056,16 @@
         <v>-7102</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.8092</v>
       </c>
       <c r="G39" t="n">
-        <v>46.24</v>
+        <v>46.2391</v>
       </c>
       <c r="H39" t="n">
-        <v>45.97</v>
+        <v>45.9668</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.27</v>
+        <v>-0.2723</v>
       </c>
     </row>
     <row r="40">
@@ -16087,16 +16087,16 @@
         <v>-4525</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.95</v>
+        <v>-0.9496</v>
       </c>
       <c r="G40" t="n">
-        <v>46.33</v>
+        <v>46.3317</v>
       </c>
       <c r="H40" t="n">
-        <v>46.07</v>
+        <v>46.0692</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.26</v>
+        <v>-0.2625</v>
       </c>
     </row>
     <row r="41">
@@ -16118,16 +16118,16 @@
         <v>-13792</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.63</v>
+        <v>-2.634</v>
       </c>
       <c r="G41" t="n">
-        <v>46.63</v>
+        <v>46.6295</v>
       </c>
       <c r="H41" t="n">
-        <v>46.77</v>
+        <v>46.7653</v>
       </c>
       <c r="I41" t="n">
-        <v>0.14</v>
+        <v>0.1358</v>
       </c>
     </row>
     <row r="42">
@@ -16149,16 +16149,16 @@
         <v>-41697</v>
       </c>
       <c r="F42" t="n">
-        <v>-3.64</v>
+        <v>-3.6432</v>
       </c>
       <c r="G42" t="n">
-        <v>46.47</v>
+        <v>46.4712</v>
       </c>
       <c r="H42" t="n">
-        <v>46.78</v>
+        <v>46.7786</v>
       </c>
       <c r="I42" t="n">
-        <v>0.31</v>
+        <v>0.3074</v>
       </c>
     </row>
   </sheetData>
